--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC75661-867A-47C9-8705-933DFF205D9D}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CEDD422-95CF-44C7-A9B7-A6394C842A41}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
     <sheet name="data_dia_len" sheetId="2" r:id="rId2"/>
     <sheet name="data_dia_diag_mat" sheetId="3" r:id="rId3"/>
     <sheet name="data_dia_diag_len" sheetId="4" r:id="rId4"/>
+    <sheet name="diag_update_mat" sheetId="5" r:id="rId5"/>
+    <sheet name="diag_update_len" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">data_dia_mat!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">diag_update_mat!$A$1:$N$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="57">
   <si>
     <t>CURSO</t>
   </si>
@@ -154,6 +157,63 @@
   <si>
     <t>TIEMPO</t>
   </si>
+  <si>
+    <t>UNIDAD ACADÉMICA</t>
+  </si>
+  <si>
+    <t>PERÍODO</t>
+  </si>
+  <si>
+    <t>ASIGNATURA</t>
+  </si>
+  <si>
+    <t>ETAPA</t>
+  </si>
+  <si>
+    <t>BÁSICA 1</t>
+  </si>
+  <si>
+    <t>MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>FINAL 2025</t>
+  </si>
+  <si>
+    <t>3BÁSICO</t>
+  </si>
+  <si>
+    <t>4BÁSICO</t>
+  </si>
+  <si>
+    <t>5BÁSICO</t>
+  </si>
+  <si>
+    <t>6BÁSICO</t>
+  </si>
+  <si>
+    <t>7BÁSICO</t>
+  </si>
+  <si>
+    <t>8BÁSICO</t>
+  </si>
+  <si>
+    <t>DIAGNOSTICO 2026</t>
+  </si>
+  <si>
+    <t>BÁSICA 2</t>
+  </si>
+  <si>
+    <t>BÁSICA SF</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>LENGUAJE</t>
+  </si>
+  <si>
+    <t>2BÁSICO</t>
+  </si>
 </sst>
 </file>
 
@@ -213,7 +273,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,8 +317,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -288,12 +354,90 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -363,6 +507,35 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6003,768 +6176,810 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="8">
+      <c r="F2" s="8">
         <v>0.78947368421052633</v>
       </c>
-      <c r="E2" s="8">
+      <c r="G2" s="8">
         <v>0.15789473684210525</v>
       </c>
-      <c r="F2" s="8">
+      <c r="H2" s="8">
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="G2" s="8">
+      <c r="I2" s="8">
         <v>0.30336052631578947</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="8">
         <v>0.32354999999999995</v>
       </c>
-      <c r="I2" s="8">
+      <c r="K2" s="8">
         <v>0.35087368421052623</v>
       </c>
-      <c r="J2" s="8">
+      <c r="L2" s="8">
         <v>0.20614999999999997</v>
       </c>
-      <c r="K2" s="8">
-        <f t="shared" ref="K2:K18" si="0">IFERROR(ROUND(AVERAGE(G2:J2),3),"")</f>
+      <c r="M2" s="8">
+        <f t="shared" ref="M2:M18" si="0">IFERROR(ROUND(AVERAGE(I2:L2),3),"")</f>
         <v>0.29599999999999999</v>
       </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
-    </row>
-    <row r="3" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8">
+      <c r="F3" s="8">
         <v>0.78378378378378377</v>
       </c>
-      <c r="E3" s="8">
+      <c r="G3" s="8">
         <v>0.13513513513513514</v>
       </c>
-      <c r="F3" s="8">
+      <c r="H3" s="8">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="G3" s="8">
+      <c r="I3" s="8">
         <v>0.28716126126126129</v>
       </c>
-      <c r="H3" s="8">
+      <c r="J3" s="8">
         <v>0.27612635135135133</v>
       </c>
-      <c r="I3" s="8">
+      <c r="K3" s="8">
         <v>0.31981621621621614</v>
       </c>
-      <c r="J3" s="8">
+      <c r="L3" s="8">
         <v>0.27477837837837832</v>
       </c>
-      <c r="K3" s="8">
+      <c r="M3" s="8">
         <f t="shared" si="0"/>
         <v>0.28899999999999998</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="12"/>
-    </row>
-    <row r="4" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+    </row>
+    <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8">
+      <c r="F4" s="8">
         <v>0.82051282051282048</v>
       </c>
-      <c r="E4" s="8">
+      <c r="G4" s="8">
         <v>0.15384615384615385</v>
       </c>
-      <c r="F4" s="8">
+      <c r="H4" s="8">
         <v>2.564102564102564E-2</v>
       </c>
-      <c r="G4" s="8">
+      <c r="I4" s="8">
         <v>0.2535606837606838</v>
       </c>
-      <c r="H4" s="8">
+      <c r="J4" s="8">
         <v>0.26935512820512814</v>
       </c>
-      <c r="I4" s="8">
+      <c r="K4" s="8">
         <v>0.37605641025641018</v>
       </c>
-      <c r="J4" s="8">
+      <c r="L4" s="8">
         <v>0.17094871794871794</v>
       </c>
-      <c r="K4" s="8">
+      <c r="M4" s="8">
         <f t="shared" si="0"/>
         <v>0.26700000000000002</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
       <c r="Q4" s="12"/>
-    </row>
-    <row r="5" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+    </row>
+    <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8">
+      <c r="F5" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="E5" s="8">
+      <c r="G5" s="8">
         <v>0.23076923076923078</v>
       </c>
-      <c r="F5" s="8">
+      <c r="H5" s="8">
         <v>0.10256410256410256</v>
       </c>
-      <c r="G5" s="8">
+      <c r="I5" s="8">
         <v>0.35221025641025638</v>
       </c>
-      <c r="H5" s="8">
+      <c r="J5" s="8">
         <v>0.34547051282051272</v>
       </c>
-      <c r="I5" s="8">
+      <c r="K5" s="8">
         <v>0.41025384615384608</v>
       </c>
-      <c r="J5" s="8">
+      <c r="L5" s="8">
         <v>0.23932051282051275</v>
       </c>
-      <c r="K5" s="8">
+      <c r="M5" s="8">
         <f t="shared" si="0"/>
         <v>0.33700000000000002</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-    </row>
-    <row r="6" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+    </row>
+    <row r="6" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="8">
+      <c r="F6" s="8">
         <v>0.70967741935483875</v>
       </c>
-      <c r="E6" s="8">
+      <c r="G6" s="8">
         <v>0.25806451612903225</v>
       </c>
-      <c r="F6" s="8">
+      <c r="H6" s="8">
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="G6" s="8">
+      <c r="I6" s="8">
         <v>0.34811720430107529</v>
       </c>
-      <c r="H6" s="8">
+      <c r="J6" s="8">
         <v>0.31876693548387081</v>
       </c>
-      <c r="I6" s="8">
+      <c r="K6" s="8">
         <v>0.41397741935483873</v>
       </c>
-      <c r="J6" s="8">
+      <c r="L6" s="8">
         <v>0.16667741935483874</v>
       </c>
-      <c r="K6" s="8">
+      <c r="M6" s="8">
         <f t="shared" si="0"/>
         <v>0.312</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
-    </row>
-    <row r="7" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+    </row>
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8">
+      <c r="F7" s="8">
         <v>0.65789473684210531</v>
       </c>
-      <c r="E7" s="8">
+      <c r="G7" s="8">
         <v>0.21052631578947367</v>
       </c>
-      <c r="F7" s="8">
+      <c r="H7" s="8">
         <v>0.13157894736842105</v>
       </c>
-      <c r="G7" s="8">
+      <c r="I7" s="8">
         <v>0.40351315789473696</v>
       </c>
-      <c r="H7" s="8">
+      <c r="J7" s="8">
         <v>0.3520375</v>
       </c>
-      <c r="I7" s="8">
+      <c r="K7" s="8">
         <v>0.36402368421052622</v>
       </c>
-      <c r="J7" s="8">
+      <c r="L7" s="8">
         <v>0.22368947368421049</v>
       </c>
-      <c r="K7" s="8">
+      <c r="M7" s="8">
         <f t="shared" si="0"/>
         <v>0.33600000000000002</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
-    </row>
-    <row r="8" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+    </row>
+    <row r="8" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8">
+      <c r="F8" s="8">
         <v>0.875</v>
       </c>
-      <c r="E8" s="8">
+      <c r="G8" s="8">
         <v>0.125</v>
       </c>
-      <c r="F8" s="8">
+      <c r="H8" s="8">
         <v>0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="I8" s="8">
         <v>0.23958194444444444</v>
       </c>
-      <c r="H8" s="8">
+      <c r="J8" s="8">
         <v>0.25530729166666666</v>
       </c>
-      <c r="I8" s="8">
+      <c r="K8" s="8">
         <v>0.27082499999999993</v>
       </c>
-      <c r="J8" s="8">
+      <c r="L8" s="8">
         <v>0.13195000000000001</v>
       </c>
-      <c r="K8" s="8">
+      <c r="M8" s="8">
         <f t="shared" si="0"/>
         <v>0.224</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
-    </row>
-    <row r="9" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+    </row>
+    <row r="9" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="F9" s="8">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E9" s="8">
+      <c r="G9" s="8">
         <v>0.13333333333333333</v>
       </c>
-      <c r="F9" s="8">
+      <c r="H9" s="8">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="G9" s="8">
+      <c r="I9" s="8">
         <v>0.29444222222222222</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="8">
         <v>0.23080666666666663</v>
       </c>
-      <c r="I9" s="8">
+      <c r="K9" s="8">
         <v>0.29999666666666663</v>
       </c>
-      <c r="J9" s="8">
+      <c r="L9" s="8">
         <v>0.22778666666666667</v>
       </c>
-      <c r="K9" s="8">
+      <c r="M9" s="8">
         <f t="shared" si="0"/>
         <v>0.26300000000000001</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
       <c r="Q9" s="12"/>
-    </row>
-    <row r="10" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+    </row>
+    <row r="10" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="8">
+      <c r="F10" s="8">
         <v>0.86111111111111116</v>
       </c>
-      <c r="E10" s="8">
+      <c r="G10" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F10" s="8">
+      <c r="H10" s="8">
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="G10" s="8">
+      <c r="I10" s="8">
         <v>0.3254277777777777</v>
       </c>
-      <c r="H10" s="8">
+      <c r="J10" s="8">
         <v>0.30392222222222215</v>
       </c>
-      <c r="I10" s="8">
+      <c r="K10" s="8">
         <v>0.3125</v>
       </c>
-      <c r="J10" s="8">
+      <c r="L10" s="8">
         <v>0.31111111111111112</v>
       </c>
-      <c r="K10" s="8">
+      <c r="M10" s="8">
         <f t="shared" si="0"/>
         <v>0.313</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-    </row>
-    <row r="11" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+    </row>
+    <row r="11" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="8">
+      <c r="F11" s="8">
         <v>0.69696969696969702</v>
       </c>
-      <c r="E11" s="8">
+      <c r="G11" s="8">
         <v>0.24242424242424243</v>
       </c>
-      <c r="F11" s="8">
+      <c r="H11" s="8">
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="G11" s="8">
+      <c r="I11" s="8">
         <v>0.35411414141414133</v>
       </c>
-      <c r="H11" s="8">
+      <c r="J11" s="8">
         <v>0.32798181818181815</v>
       </c>
-      <c r="I11" s="8">
+      <c r="K11" s="8">
         <v>0.43181818181818182</v>
       </c>
-      <c r="J11" s="8">
+      <c r="L11" s="8">
         <v>0.27272727272727271</v>
       </c>
-      <c r="K11" s="8">
+      <c r="M11" s="8">
         <f t="shared" si="0"/>
         <v>0.34699999999999998</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
-    </row>
-    <row r="12" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+    </row>
+    <row r="12" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="8">
+      <c r="F12" s="8">
         <v>0.625</v>
       </c>
-      <c r="E12" s="8">
+      <c r="G12" s="8">
         <v>0.34375</v>
       </c>
-      <c r="F12" s="8">
+      <c r="H12" s="8">
         <v>3.125E-2</v>
       </c>
-      <c r="G12" s="8">
+      <c r="I12" s="8">
         <v>0.35206458333333329</v>
       </c>
-      <c r="H12" s="8">
+      <c r="J12" s="8">
         <v>0.31249999999999994</v>
       </c>
-      <c r="I12" s="8">
+      <c r="K12" s="8">
         <v>0.4296875</v>
       </c>
-      <c r="J12" s="8">
+      <c r="L12" s="8">
         <v>0.27500000000000002</v>
       </c>
-      <c r="K12" s="8">
+      <c r="M12" s="8">
         <f t="shared" si="0"/>
         <v>0.34200000000000003</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-    </row>
-    <row r="13" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+    </row>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="8">
+      <c r="F13" s="8">
         <v>0.8125</v>
       </c>
-      <c r="E13" s="8">
+      <c r="G13" s="8">
         <v>0.1875</v>
       </c>
-      <c r="F13" s="8">
+      <c r="H13" s="8">
         <v>0</v>
       </c>
-      <c r="G13" s="8">
+      <c r="I13" s="8">
         <v>0.25434999999999997</v>
       </c>
-      <c r="H13" s="8">
+      <c r="J13" s="8">
         <v>0.22057499999999997</v>
       </c>
-      <c r="I13" s="8">
+      <c r="K13" s="8">
         <v>0.390625</v>
       </c>
-      <c r="J13" s="8">
+      <c r="L13" s="8">
         <v>0.3125</v>
       </c>
-      <c r="K13" s="8">
+      <c r="M13" s="8">
         <f t="shared" si="0"/>
         <v>0.29499999999999998</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-    </row>
-    <row r="14" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+    </row>
+    <row r="14" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="8">
+      <c r="F14" s="8">
         <v>0.76</v>
       </c>
-      <c r="E14" s="8">
+      <c r="G14" s="8">
         <v>0.24</v>
       </c>
-      <c r="F14" s="8">
+      <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="G14" s="8">
+      <c r="I14" s="8">
         <v>0.30860800000000005</v>
       </c>
-      <c r="H14" s="8">
+      <c r="J14" s="8">
         <v>0.29881599999999997</v>
       </c>
-      <c r="I14" s="8">
+      <c r="K14" s="8">
         <v>0.44</v>
       </c>
-      <c r="J14" s="8">
+      <c r="L14" s="8">
         <v>0.40799999999999997</v>
       </c>
-      <c r="K14" s="8">
+      <c r="M14" s="8">
         <f t="shared" si="0"/>
         <v>0.36399999999999999</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
-    </row>
-    <row r="15" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+    </row>
+    <row r="15" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="8">
+      <c r="F15" s="8">
         <v>0.53125</v>
       </c>
-      <c r="E15" s="8">
+      <c r="G15" s="8">
         <v>0.375</v>
       </c>
-      <c r="F15" s="8">
+      <c r="H15" s="8">
         <v>9.375E-2</v>
       </c>
-      <c r="G15" s="8">
+      <c r="I15" s="8">
         <v>0.41018958333333322</v>
       </c>
-      <c r="H15" s="8">
+      <c r="J15" s="8">
         <v>0.35936562500000008</v>
       </c>
-      <c r="I15" s="8">
+      <c r="K15" s="8">
         <v>0.4375</v>
       </c>
-      <c r="J15" s="8">
+      <c r="L15" s="8">
         <v>0.33750000000000002</v>
       </c>
-      <c r="K15" s="8">
+      <c r="M15" s="8">
         <f t="shared" si="0"/>
         <v>0.38600000000000001</v>
       </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
-    </row>
-    <row r="16" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+    </row>
+    <row r="16" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="8">
+      <c r="F16" s="8">
         <v>0.3611111111111111</v>
       </c>
-      <c r="E16" s="8">
+      <c r="G16" s="8">
         <v>0.55555555555555558</v>
       </c>
-      <c r="F16" s="8">
+      <c r="H16" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G16" s="8">
+      <c r="I16" s="8">
         <v>0.42199907407407411</v>
       </c>
-      <c r="H16" s="8">
+      <c r="J16" s="8">
         <v>0.4019638888888889</v>
       </c>
-      <c r="I16" s="8">
+      <c r="K16" s="8">
         <v>0.53472222222222221</v>
       </c>
-      <c r="J16" s="8">
+      <c r="L16" s="8">
         <v>0.28333333333333333</v>
       </c>
-      <c r="K16" s="8">
+      <c r="M16" s="8">
         <f t="shared" si="0"/>
         <v>0.41099999999999998</v>
       </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
-    </row>
-    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="8">
-        <f t="shared" ref="D17:J18" si="1">IFERROR(AVERAGEIFS(D$2:D$16,$B$2:$B$16,$B17,$C$2:$C$16,$C17),"")</f>
+      <c r="F17" s="8">
+        <f t="shared" ref="F17:L18" si="1">IFERROR(AVERAGEIFS(F$2:F$16,$D$2:$D$16,$D17,$E$2:$E$16,$E17),"")</f>
         <v>0.7670428055880093</v>
       </c>
-      <c r="E17" s="8">
+      <c r="G17" s="8">
         <f t="shared" si="1"/>
         <v>0.17557117773055803</v>
       </c>
-      <c r="F17" s="8">
+      <c r="H17" s="8">
         <f t="shared" si="1"/>
         <v>5.7386016681432631E-2</v>
       </c>
-      <c r="G17" s="8">
+      <c r="I17" s="8">
         <f t="shared" si="1"/>
         <v>0.31024340707630871</v>
       </c>
-      <c r="H17" s="8">
+      <c r="J17" s="8">
         <f t="shared" si="1"/>
         <v>0.29642754827427453</v>
       </c>
-      <c r="I17" s="8">
+      <c r="K17" s="8">
         <f t="shared" si="1"/>
         <v>0.3507278658836287</v>
       </c>
-      <c r="J17" s="8">
+      <c r="L17" s="8">
         <f t="shared" si="1"/>
         <v>0.20516264610666562</v>
       </c>
-      <c r="K17" s="8">
+      <c r="M17" s="8">
         <f t="shared" si="0"/>
         <v>0.29099999999999998</v>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
-    </row>
-    <row r="18" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+    </row>
+    <row r="18" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="8">
+      <c r="F18" s="8">
         <f t="shared" si="1"/>
         <v>0.66399170274170261</v>
       </c>
-      <c r="E18" s="8">
+      <c r="G18" s="8">
         <f t="shared" si="1"/>
         <v>0.28965187590187591</v>
       </c>
-      <c r="F18" s="8">
+      <c r="H18" s="8">
         <f t="shared" si="1"/>
         <v>4.635642135642136E-2</v>
       </c>
-      <c r="G18" s="8">
+      <c r="I18" s="8">
         <f t="shared" si="1"/>
         <v>0.34667902284752278</v>
       </c>
-      <c r="H18" s="8">
+      <c r="J18" s="8">
         <f t="shared" si="1"/>
         <v>0.31787493632756136</v>
       </c>
-      <c r="I18" s="8">
+      <c r="K18" s="8">
         <f t="shared" si="1"/>
         <v>0.42526470057720062</v>
       </c>
-      <c r="J18" s="8">
+      <c r="L18" s="8">
         <f t="shared" si="1"/>
         <v>0.31431024531024526</v>
       </c>
-      <c r="K18" s="8">
+      <c r="M18" s="8">
         <f t="shared" si="0"/>
         <v>0.35099999999999998</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="K2 K3:K18" formulaRange="1"/>
+    <ignoredError sqref="M2 M3:M18" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7393,4 +7608,3184 @@
     <ignoredError sqref="J2:J18" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54D2E6-D3E1-4CCD-A700-1303E31935A9}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.80408163265306132</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0.73469387755102045</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M2" s="15">
+        <v>0.88436530612244912</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0.81318571428571418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.5674688888888888</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0.65926666666666678</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="N3" s="15">
+        <v>0.60313111111111128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H4" s="15">
+        <v>6.25E-2</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.51282708333333316</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0.63195208333333341</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0.34166666666666662</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="N4" s="15">
+        <v>0.57228749999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.46913580246913578</v>
+      </c>
+      <c r="H5" s="15">
+        <v>2.4691358024691357E-2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0.44664691358024688</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0.38271234567901224</v>
+      </c>
+      <c r="K5" s="15">
+        <v>0.55556419753086439</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0.31790123456790126</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0.37036543209876532</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0.41463703703703692</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="H6" s="15">
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0.35164693877551018</v>
+      </c>
+      <c r="J6" s="15">
+        <v>0.70408163265306134</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0.28571428571428575</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0.50510204081632648</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0.46216326530612245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.703125</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.296875</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0.36433125</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.33158437499999999</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0.359375</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0.32031093749999989</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0.34389999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.20370370370370369</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.56166084656084658</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.57407407407407407</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.58642407407407415</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.66203703703703709</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0.73148148148148151</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0.59564259259259256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.22950819672131148</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.39344262295081966</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.37704918032786883</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0.48794918032786905</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.57650245901639341</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0.31147540983606559</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0.63934426229508201</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0.68032786885245899</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0.53711147540983606</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G10" s="15">
+        <v>0.54285714285714282</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0.39115553571428568</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.38214285714285717</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0.56785714285714284</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0.6753985714285714</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0.46339714285714295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.36538461538461536</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0.50333830128205148</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0.56923076923076921</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0.69872788461538482</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0.53526153846153857</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0.453125</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0.53565576923076941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.43103448275862066</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.36206896551724138</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0.45852241379310343</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.35991379310344823</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0.54885603448275877</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0.44181034482758619</v>
+      </c>
+      <c r="N12" s="15">
+        <v>0.45297068965517229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.27710843373493976</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0.40963855421686746</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0.31325301204819278</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0.54217068273092373</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.45180542168674698</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.46586325301204817</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0.57028192771084341</v>
+      </c>
+      <c r="N13" s="15">
+        <v>0.5172674698795181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="15">
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0.46296296296296297</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0.74814814814814812</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.75925925925925919</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.71296296296296291</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0.70372037037037061</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0.75516851851851829</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="H15" s="15">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0.49206000000000005</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0.77777777777777768</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0.54074222222222201</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="N15" s="15">
+        <v>0.55323111111111101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0.33870967741935482</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0.56451612903225812</v>
+      </c>
+      <c r="H16" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0.47953064516129035</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.63441290322580657</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0.62096774193548387</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0.3612903225806452</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0.66935483870967749</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0.55311290322580631</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.38805970149253732</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0.55223880597014929</v>
+      </c>
+      <c r="H17" s="15">
+        <v>5.9701492537313432E-2</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0.52344925373134332</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0.46268059701492542</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0.59204925373134332</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0.30970149253731344</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0.56716417910447769</v>
+      </c>
+      <c r="N17" s="15">
+        <v>0.49101343283582083</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0.46314374999999991</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0.55729166666666663</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0.31770833333333331</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0.1875</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0.5859375</v>
+      </c>
+      <c r="N18" s="15">
+        <v>0.4223229166666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0.45680999999999977</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.47962499999999997</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0.50277500000000008</v>
+      </c>
+      <c r="N19" s="15">
+        <v>0.45980666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.58695652173913049</v>
+      </c>
+      <c r="I20" s="15">
+        <v>0.60874720496894386</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.45652173913043476</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0.69565434782608704</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0.61956521739130432</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0.61596956521739121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0.32142857142857145</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0.43941862244897967</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0.52455357142857151</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0.63392857142857151</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0.48342321428571433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0.33269192307692314</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.34423076923076917</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0.56153846153846154</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0.58632615384615383</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0.39743589743589747</v>
+      </c>
+      <c r="N22" s="15">
+        <v>0.41245999999999972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.27692307692307694</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0.26153846153846155</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0.4327589743589742</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.48</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.61538846153846161</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0.49487615384615391</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0.52884615384615385</v>
+      </c>
+      <c r="N23" s="15">
+        <v>0.48882923076923068</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.41891891891891891</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0.43243243243243246</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0.14864864864864866</v>
+      </c>
+      <c r="I24" s="15">
+        <v>0.45975810810810808</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.33614864864864863</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.51239256756756768</v>
+      </c>
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0.42539324324324318</v>
+      </c>
+      <c r="N24" s="15">
+        <v>0.43634324324324325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.19178082191780821</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0.46575342465753422</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0.34246575342465752</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0.55479497716894977</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0.54452191780821912</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0.51598082191780814</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0.54490091324200907</v>
+      </c>
+      <c r="N25" s="15">
+        <v>0.54200821917808217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.13414634146341464</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0.52439024390243905</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0.34146341463414637</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0.63048780487804879</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.65243902439024393</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.60365853658536583</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0.68293658536585378</v>
+      </c>
+      <c r="N26" s="15">
+        <v>0.65779512195121925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0.58163265306122447</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0.31632653061224492</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0.70954795918367364</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.75510204081632648</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.81632653061224492</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0.5782326530612244</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0.60714285714285721</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0.69327142857142843</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.14166666666666666</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.64968250000000016</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0.73611583333333341</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="L28" s="15">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="M28" s="15">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="N28" s="15">
+        <v>0.69382333333333379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="15">
+        <v>0.33613445378151263</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="H29" s="15">
+        <v>9.2436974789915971E-2</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0.53391092436974796</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0.42016638655462191</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0.58823781512605045</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0.49019411764705878</v>
+      </c>
+      <c r="N29" s="15">
+        <v>0.47792521008403355</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="15">
+        <v>9.0090090090090086E-2</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0.63963963963963966</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="I30" s="15">
+        <v>0.60845945945945934</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0.83108108108108114</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0.71846846846846846</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0.55630630630630629</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0.60923423423423417</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0.66470540540540579</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="15">
+        <v>0.56302521008403361</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0.36974789915966388</v>
+      </c>
+      <c r="H31" s="15">
+        <v>6.7226890756302518E-2</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0.38462941176470578</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0.45844285714285699</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0.40336134453781514</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0.39775966386554612</v>
+      </c>
+      <c r="N31" s="15">
+        <v>0.41104789915966372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0.28378378378378377</v>
+      </c>
+      <c r="H32" s="15">
+        <v>0.47297297297297297</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0.53684034749034737</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="K32" s="15">
+        <v>0.5360364864864865</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.6283783783783784</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0.69594594594594594</v>
+      </c>
+      <c r="N32" s="15">
+        <v>0.56560135135135114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="15">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I33" s="15">
+        <v>0.58076309523809566</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0.67144062500000001</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M33" s="15">
+        <v>0.78645833333333326</v>
+      </c>
+      <c r="N33" s="15">
+        <v>0.6467197916666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.390625</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0.40625</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0.203125</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0.40278593749999997</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0.3466796875</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0.56640625</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0.56423776041666618</v>
+      </c>
+      <c r="M34" s="15">
+        <v>0.45963541666666663</v>
+      </c>
+      <c r="N34" s="15">
+        <v>0.45111718749999979</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="15">
+        <v>7.03125E-2</v>
+      </c>
+      <c r="G35" s="15">
+        <v>0.203125</v>
+      </c>
+      <c r="H35" s="15">
+        <v>0.7265625</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0.67849518229166661</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0.69687500000000002</v>
+      </c>
+      <c r="K35" s="15">
+        <v>0.77865234374999914</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0.66536875000000006</v>
+      </c>
+      <c r="M35" s="15">
+        <v>0.6845703125</v>
+      </c>
+      <c r="N35" s="15">
+        <v>0.69423203124999988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0.18548387096774194</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0.45967741935483869</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0.54448763440860215</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0.49899193548387094</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0.72580766129032237</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15">
+        <v>0.56955685483870966</v>
+      </c>
+      <c r="N36" s="15">
+        <v>0.5802459677419356</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0.19379844961240311</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="H37" s="15">
+        <v>0.4573643410852713</v>
+      </c>
+      <c r="I37" s="15">
+        <v>0.61050826873385</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0.51808604651162793</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0.53165542635658913</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15">
+        <v>0.59538888888888908</v>
+      </c>
+      <c r="N37" s="15">
+        <v>0.57171782945736438</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8147AE5B-C20B-4DEF-A7F6-B50B97C6DCC0}">
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.12</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.42</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.46</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.64833199999999991</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0.54</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0.62944600000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.38</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0.75466399999999989</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0.7018859999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="15">
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.32203389830508472</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.61016440677966088</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0.6451271186440678</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0.64406779661016955</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0.63311186440677969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.23655913978494625</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.63440860215053763</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0.58243655913978498</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0.52625698924731201</v>
+      </c>
+      <c r="K5" s="15">
+        <v>0.40591397849462368</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0.50486989247311842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.22033898305084745</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.50847457627118642</v>
+      </c>
+      <c r="H6" s="15">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0.70847457627118648</v>
+      </c>
+      <c r="J6" s="15">
+        <v>0.56645593220338974</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0.42584745762711862</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0.56692881355932234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.21621621621621623</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.68918918918918914</v>
+      </c>
+      <c r="H7" s="15">
+        <v>9.45945945945946E-2</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0.66891891891891886</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.56543108108108098</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0.40829594594594587</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0.54754459459459459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.29268292682926828</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.31707317073170732</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.68699268292682936</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.56585365853658542</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.40243902439024387</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.55176097560975623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.6153883333333332</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0.48179666666666665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="G10" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0.84676935483870963</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.72473870967741949</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0.70125483870967753</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.62666666666666671</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0.5964506666666668</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0.6310399999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.26168224299065418</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.44859813084112149</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.28971962616822428</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0.52336448598130847</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.4972943925233646</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0.51635514018691586</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0.5123392523364485</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.17741935483870969</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0.40322580645161288</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0.56451612903225812</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.51867419354838729</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.59193548387096773</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0.55837258064516138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.1875</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0.74687499999999996</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.54874999999999996</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.44270625000000008</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0.57944249999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="15">
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0.79215686274509811</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.7058843137254901</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0.57352941176470584</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0.69052352941176465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="15">
+        <v>8.1632653061224483E-2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0.65306122448979587</v>
+      </c>
+      <c r="H16" s="15">
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0.67346938775510212</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.68571836734693892</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0.18877551020408162</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0.51598775510204087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.125</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0.5892857142857143</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0.58928214285714275</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0.63392857142857151</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0.41517857142857145</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0.54613035714285718</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.16981132075471697</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.60377358490566035</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0.6981094339622641</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0.61820377358490541</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0.44339622641509435</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0.58657735849056603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.21818181818181817</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0.58181818181818179</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0.67636363636363639</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.51579818181818204</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0.38636363636363635</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0.52617272727272735</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.26865671641791045</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0.62686567164179108</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="I20" s="15">
+        <v>0.56343283582089554</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.57816119402985078</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0.40831492537313435</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0.51663880597014922</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0.65</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0.65833499999999989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0.66530612244897958</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.67739591836734681</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0.33673469387755106</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0.55981428571428582</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0.79737843137254882</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.7058803921568626</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0.62526078431372545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.25423728813559321</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0.30508474576271188</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0.44067796610169491</v>
+      </c>
+      <c r="I24" s="15">
+        <v>0.71398305084745761</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.60565084745762698</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.3135593220338983</v>
+      </c>
+      <c r="L24" s="15">
+        <v>0.54439830508474574</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.28169014084507044</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0.40845070422535212</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0.30985915492957744</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0.59859154929577463</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0.52557464788732366</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0.42957746478873238</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0.51792112676056345</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.39344262295081966</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0.26229508196721313</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0.34426229508196721</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0.56147540983606559</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.5125065573770492</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.44098360655737706</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0.50499344262295087</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.13580246913580246</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0.34567901234567899</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.41357777777777771</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0.5971209876543212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.28048780487804881</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0.3048780487804878</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0.41463414634146339</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.67804878048780493</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0.55996219512195122</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.52134146341463417</v>
+      </c>
+      <c r="L28" s="15">
+        <v>0.58644390243902422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1.0309278350515464E-2</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0.51546391752577314</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0.47422680412371132</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0.72989690721649481</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0.76151443298969068</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0.70103092783505161</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0.7308154639175255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="15">
+        <v>0.12844036697247707</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0.47706422018348627</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0.39449541284403672</v>
+      </c>
+      <c r="I30" s="15">
+        <v>0.64067247706422026</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0.64793577981651385</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0.71330275229357798</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0.66730550458715587</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="15">
+        <v>4.807692307692308E-2</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0.70192307692307687</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0.69390480769230767</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0.64084038461538451</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0.64903846153846156</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0.66125865384615423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.11214953271028037</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0.52336448598130836</v>
+      </c>
+      <c r="H32" s="15">
+        <v>0.3644859813084112</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0.71962616822429903</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0.63501962616822438</v>
+      </c>
+      <c r="K32" s="15">
+        <v>0.5490654205607477</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.63457289719626153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="15">
+        <v>0.1484375</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0.734375</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0.1171875</v>
+      </c>
+      <c r="I33" s="15">
+        <v>0.75390625</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0.61471718750000004</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0.50055859375</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0.62306249999999974</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.35802469135802467</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0.2839506172839506</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0.35802469135802467</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0.66460740740740731</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0.57901234567901239</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0.3271604938271605</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0.52360000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="15">
+        <v>0.32876712328767121</v>
+      </c>
+      <c r="G35" s="15">
+        <v>0.26027397260273971</v>
+      </c>
+      <c r="H35" s="15">
+        <v>0.41095890410958902</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0.57808219178082187</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0.63857397260273929</v>
+      </c>
+      <c r="K35" s="15">
+        <v>0.36986301369863012</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0.52884109589041084</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="15">
+        <v>1.0101010101010102E-2</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.14141414141414141</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0.84848484848484851</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0.88046767676767668</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0.77441414141414144</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0.6767676767676768</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0.77722323232323265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.2076923076923077</v>
+      </c>
+      <c r="H37" s="15">
+        <v>0.63846153846153841</v>
+      </c>
+      <c r="I37" s="15">
+        <v>0.75096153846153835</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0.6215376923076924</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0.65192307692307694</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0.67480692307692325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="15">
+        <v>7.5471698113207544E-2</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="H38" s="15">
+        <v>0.68867924528301883</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0.72169811320754718</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0.70257830188679238</v>
+      </c>
+      <c r="K38" s="15">
+        <v>0.68985849056603765</v>
+      </c>
+      <c r="L38" s="15">
+        <v>0.70471226415094324</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="15">
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0.37606837606837606</v>
+      </c>
+      <c r="H39" s="15">
+        <v>0.36752136752136755</v>
+      </c>
+      <c r="I39" s="15">
+        <v>0.55982905982905984</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0.48133504273504263</v>
+      </c>
+      <c r="K39" s="15">
+        <v>0.51452991452991459</v>
+      </c>
+      <c r="L39" s="15">
+        <v>0.51856666666666673</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="15">
+        <v>0.28440366972477066</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="H40" s="15">
+        <v>0.3669724770642202</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0.65137614678899081</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0.37156055045871567</v>
+      </c>
+      <c r="L40" s="15">
+        <v>0.5122321100917433</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC75661-867A-47C9-8705-933DFF205D9D}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA12E562-F759-5D3E-B843-43B213C11C83}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
@@ -382,10 +382,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -8,18 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA12E562-F759-5D3E-B843-43B213C11C83}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CEDD422-95CF-44C7-A9B7-A6394C842A41}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
     <sheet name="data_dia_len" sheetId="2" r:id="rId2"/>
     <sheet name="data_dia_diag_mat" sheetId="3" r:id="rId3"/>
     <sheet name="data_dia_diag_len" sheetId="4" r:id="rId4"/>
+    <sheet name="diag_update_mat" sheetId="5" r:id="rId5"/>
+    <sheet name="diag_update_len" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">data_dia_mat!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">diag_update_mat!$A$1:$N$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="57">
   <si>
     <t>CURSO</t>
   </si>
@@ -154,6 +157,63 @@
   <si>
     <t>TIEMPO</t>
   </si>
+  <si>
+    <t>UNIDAD ACADÉMICA</t>
+  </si>
+  <si>
+    <t>PERÍODO</t>
+  </si>
+  <si>
+    <t>ASIGNATURA</t>
+  </si>
+  <si>
+    <t>ETAPA</t>
+  </si>
+  <si>
+    <t>BÁSICA 1</t>
+  </si>
+  <si>
+    <t>MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>FINAL 2025</t>
+  </si>
+  <si>
+    <t>3BÁSICO</t>
+  </si>
+  <si>
+    <t>4BÁSICO</t>
+  </si>
+  <si>
+    <t>5BÁSICO</t>
+  </si>
+  <si>
+    <t>6BÁSICO</t>
+  </si>
+  <si>
+    <t>7BÁSICO</t>
+  </si>
+  <si>
+    <t>8BÁSICO</t>
+  </si>
+  <si>
+    <t>DIAGNOSTICO 2026</t>
+  </si>
+  <si>
+    <t>BÁSICA 2</t>
+  </si>
+  <si>
+    <t>BÁSICA SF</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>LENGUAJE</t>
+  </si>
+  <si>
+    <t>2BÁSICO</t>
+  </si>
 </sst>
 </file>
 
@@ -213,7 +273,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,8 +317,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -288,12 +354,90 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,6 +508,35 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,6 +553,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5999,768 +6176,810 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="8">
+      <c r="F2" s="8">
         <v>0.78947368421052633</v>
       </c>
-      <c r="E2" s="8">
+      <c r="G2" s="8">
         <v>0.15789473684210525</v>
       </c>
-      <c r="F2" s="8">
+      <c r="H2" s="8">
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="G2" s="8">
+      <c r="I2" s="8">
         <v>0.30336052631578947</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="8">
         <v>0.32354999999999995</v>
       </c>
-      <c r="I2" s="8">
+      <c r="K2" s="8">
         <v>0.35087368421052623</v>
       </c>
-      <c r="J2" s="8">
+      <c r="L2" s="8">
         <v>0.20614999999999997</v>
       </c>
-      <c r="K2" s="8">
-        <f t="shared" ref="K2:K18" si="0">IFERROR(ROUND(AVERAGE(G2:J2),3),"")</f>
+      <c r="M2" s="8">
+        <f t="shared" ref="M2:M18" si="0">IFERROR(ROUND(AVERAGE(I2:L2),3),"")</f>
         <v>0.29599999999999999</v>
       </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
-    </row>
-    <row r="3" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8">
+      <c r="F3" s="8">
         <v>0.78378378378378377</v>
       </c>
-      <c r="E3" s="8">
+      <c r="G3" s="8">
         <v>0.13513513513513514</v>
       </c>
-      <c r="F3" s="8">
+      <c r="H3" s="8">
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="G3" s="8">
+      <c r="I3" s="8">
         <v>0.28716126126126129</v>
       </c>
-      <c r="H3" s="8">
+      <c r="J3" s="8">
         <v>0.27612635135135133</v>
       </c>
-      <c r="I3" s="8">
+      <c r="K3" s="8">
         <v>0.31981621621621614</v>
       </c>
-      <c r="J3" s="8">
+      <c r="L3" s="8">
         <v>0.27477837837837832</v>
       </c>
-      <c r="K3" s="8">
+      <c r="M3" s="8">
         <f t="shared" si="0"/>
         <v>0.28899999999999998</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="12"/>
-    </row>
-    <row r="4" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+    </row>
+    <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8">
+      <c r="F4" s="8">
         <v>0.82051282051282048</v>
       </c>
-      <c r="E4" s="8">
+      <c r="G4" s="8">
         <v>0.15384615384615385</v>
       </c>
-      <c r="F4" s="8">
+      <c r="H4" s="8">
         <v>2.564102564102564E-2</v>
       </c>
-      <c r="G4" s="8">
+      <c r="I4" s="8">
         <v>0.2535606837606838</v>
       </c>
-      <c r="H4" s="8">
+      <c r="J4" s="8">
         <v>0.26935512820512814</v>
       </c>
-      <c r="I4" s="8">
+      <c r="K4" s="8">
         <v>0.37605641025641018</v>
       </c>
-      <c r="J4" s="8">
+      <c r="L4" s="8">
         <v>0.17094871794871794</v>
       </c>
-      <c r="K4" s="8">
+      <c r="M4" s="8">
         <f t="shared" si="0"/>
         <v>0.26700000000000002</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="12"/>
       <c r="Q4" s="12"/>
-    </row>
-    <row r="5" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+    </row>
+    <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8">
+      <c r="F5" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="E5" s="8">
+      <c r="G5" s="8">
         <v>0.23076923076923078</v>
       </c>
-      <c r="F5" s="8">
+      <c r="H5" s="8">
         <v>0.10256410256410256</v>
       </c>
-      <c r="G5" s="8">
+      <c r="I5" s="8">
         <v>0.35221025641025638</v>
       </c>
-      <c r="H5" s="8">
+      <c r="J5" s="8">
         <v>0.34547051282051272</v>
       </c>
-      <c r="I5" s="8">
+      <c r="K5" s="8">
         <v>0.41025384615384608</v>
       </c>
-      <c r="J5" s="8">
+      <c r="L5" s="8">
         <v>0.23932051282051275</v>
       </c>
-      <c r="K5" s="8">
+      <c r="M5" s="8">
         <f t="shared" si="0"/>
         <v>0.33700000000000002</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-    </row>
-    <row r="6" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+    </row>
+    <row r="6" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="8">
+      <c r="F6" s="8">
         <v>0.70967741935483875</v>
       </c>
-      <c r="E6" s="8">
+      <c r="G6" s="8">
         <v>0.25806451612903225</v>
       </c>
-      <c r="F6" s="8">
+      <c r="H6" s="8">
         <v>3.2258064516129031E-2</v>
       </c>
-      <c r="G6" s="8">
+      <c r="I6" s="8">
         <v>0.34811720430107529</v>
       </c>
-      <c r="H6" s="8">
+      <c r="J6" s="8">
         <v>0.31876693548387081</v>
       </c>
-      <c r="I6" s="8">
+      <c r="K6" s="8">
         <v>0.41397741935483873</v>
       </c>
-      <c r="J6" s="8">
+      <c r="L6" s="8">
         <v>0.16667741935483874</v>
       </c>
-      <c r="K6" s="8">
+      <c r="M6" s="8">
         <f t="shared" si="0"/>
         <v>0.312</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
-    </row>
-    <row r="7" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+    </row>
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8">
+      <c r="F7" s="8">
         <v>0.65789473684210531</v>
       </c>
-      <c r="E7" s="8">
+      <c r="G7" s="8">
         <v>0.21052631578947367</v>
       </c>
-      <c r="F7" s="8">
+      <c r="H7" s="8">
         <v>0.13157894736842105</v>
       </c>
-      <c r="G7" s="8">
+      <c r="I7" s="8">
         <v>0.40351315789473696</v>
       </c>
-      <c r="H7" s="8">
+      <c r="J7" s="8">
         <v>0.3520375</v>
       </c>
-      <c r="I7" s="8">
+      <c r="K7" s="8">
         <v>0.36402368421052622</v>
       </c>
-      <c r="J7" s="8">
+      <c r="L7" s="8">
         <v>0.22368947368421049</v>
       </c>
-      <c r="K7" s="8">
+      <c r="M7" s="8">
         <f t="shared" si="0"/>
         <v>0.33600000000000002</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
-    </row>
-    <row r="8" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+    </row>
+    <row r="8" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8">
+      <c r="F8" s="8">
         <v>0.875</v>
       </c>
-      <c r="E8" s="8">
+      <c r="G8" s="8">
         <v>0.125</v>
       </c>
-      <c r="F8" s="8">
+      <c r="H8" s="8">
         <v>0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="I8" s="8">
         <v>0.23958194444444444</v>
       </c>
-      <c r="H8" s="8">
+      <c r="J8" s="8">
         <v>0.25530729166666666</v>
       </c>
-      <c r="I8" s="8">
+      <c r="K8" s="8">
         <v>0.27082499999999993</v>
       </c>
-      <c r="J8" s="8">
+      <c r="L8" s="8">
         <v>0.13195000000000001</v>
       </c>
-      <c r="K8" s="8">
+      <c r="M8" s="8">
         <f t="shared" si="0"/>
         <v>0.224</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
-    </row>
-    <row r="9" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+    </row>
+    <row r="9" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="F9" s="8">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E9" s="8">
+      <c r="G9" s="8">
         <v>0.13333333333333333</v>
       </c>
-      <c r="F9" s="8">
+      <c r="H9" s="8">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="G9" s="8">
+      <c r="I9" s="8">
         <v>0.29444222222222222</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="8">
         <v>0.23080666666666663</v>
       </c>
-      <c r="I9" s="8">
+      <c r="K9" s="8">
         <v>0.29999666666666663</v>
       </c>
-      <c r="J9" s="8">
+      <c r="L9" s="8">
         <v>0.22778666666666667</v>
       </c>
-      <c r="K9" s="8">
+      <c r="M9" s="8">
         <f t="shared" si="0"/>
         <v>0.26300000000000001</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
       <c r="Q9" s="12"/>
-    </row>
-    <row r="10" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+    </row>
+    <row r="10" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="8">
+      <c r="F10" s="8">
         <v>0.86111111111111116</v>
       </c>
-      <c r="E10" s="8">
+      <c r="G10" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F10" s="8">
+      <c r="H10" s="8">
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="G10" s="8">
+      <c r="I10" s="8">
         <v>0.3254277777777777</v>
       </c>
-      <c r="H10" s="8">
+      <c r="J10" s="8">
         <v>0.30392222222222215</v>
       </c>
-      <c r="I10" s="8">
+      <c r="K10" s="8">
         <v>0.3125</v>
       </c>
-      <c r="J10" s="8">
+      <c r="L10" s="8">
         <v>0.31111111111111112</v>
       </c>
-      <c r="K10" s="8">
+      <c r="M10" s="8">
         <f t="shared" si="0"/>
         <v>0.313</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-    </row>
-    <row r="11" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+    </row>
+    <row r="11" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="8">
+      <c r="F11" s="8">
         <v>0.69696969696969702</v>
       </c>
-      <c r="E11" s="8">
+      <c r="G11" s="8">
         <v>0.24242424242424243</v>
       </c>
-      <c r="F11" s="8">
+      <c r="H11" s="8">
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="G11" s="8">
+      <c r="I11" s="8">
         <v>0.35411414141414133</v>
       </c>
-      <c r="H11" s="8">
+      <c r="J11" s="8">
         <v>0.32798181818181815</v>
       </c>
-      <c r="I11" s="8">
+      <c r="K11" s="8">
         <v>0.43181818181818182</v>
       </c>
-      <c r="J11" s="8">
+      <c r="L11" s="8">
         <v>0.27272727272727271</v>
       </c>
-      <c r="K11" s="8">
+      <c r="M11" s="8">
         <f t="shared" si="0"/>
         <v>0.34699999999999998</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
-    </row>
-    <row r="12" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+    </row>
+    <row r="12" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="8">
+      <c r="F12" s="8">
         <v>0.625</v>
       </c>
-      <c r="E12" s="8">
+      <c r="G12" s="8">
         <v>0.34375</v>
       </c>
-      <c r="F12" s="8">
+      <c r="H12" s="8">
         <v>3.125E-2</v>
       </c>
-      <c r="G12" s="8">
+      <c r="I12" s="8">
         <v>0.35206458333333329</v>
       </c>
-      <c r="H12" s="8">
+      <c r="J12" s="8">
         <v>0.31249999999999994</v>
       </c>
-      <c r="I12" s="8">
+      <c r="K12" s="8">
         <v>0.4296875</v>
       </c>
-      <c r="J12" s="8">
+      <c r="L12" s="8">
         <v>0.27500000000000002</v>
       </c>
-      <c r="K12" s="8">
+      <c r="M12" s="8">
         <f t="shared" si="0"/>
         <v>0.34200000000000003</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-    </row>
-    <row r="13" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+    </row>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="8">
+      <c r="F13" s="8">
         <v>0.8125</v>
       </c>
-      <c r="E13" s="8">
+      <c r="G13" s="8">
         <v>0.1875</v>
       </c>
-      <c r="F13" s="8">
+      <c r="H13" s="8">
         <v>0</v>
       </c>
-      <c r="G13" s="8">
+      <c r="I13" s="8">
         <v>0.25434999999999997</v>
       </c>
-      <c r="H13" s="8">
+      <c r="J13" s="8">
         <v>0.22057499999999997</v>
       </c>
-      <c r="I13" s="8">
+      <c r="K13" s="8">
         <v>0.390625</v>
       </c>
-      <c r="J13" s="8">
+      <c r="L13" s="8">
         <v>0.3125</v>
       </c>
-      <c r="K13" s="8">
+      <c r="M13" s="8">
         <f t="shared" si="0"/>
         <v>0.29499999999999998</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-    </row>
-    <row r="14" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+    </row>
+    <row r="14" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="8">
+      <c r="F14" s="8">
         <v>0.76</v>
       </c>
-      <c r="E14" s="8">
+      <c r="G14" s="8">
         <v>0.24</v>
       </c>
-      <c r="F14" s="8">
+      <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="G14" s="8">
+      <c r="I14" s="8">
         <v>0.30860800000000005</v>
       </c>
-      <c r="H14" s="8">
+      <c r="J14" s="8">
         <v>0.29881599999999997</v>
       </c>
-      <c r="I14" s="8">
+      <c r="K14" s="8">
         <v>0.44</v>
       </c>
-      <c r="J14" s="8">
+      <c r="L14" s="8">
         <v>0.40799999999999997</v>
       </c>
-      <c r="K14" s="8">
+      <c r="M14" s="8">
         <f t="shared" si="0"/>
         <v>0.36399999999999999</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
-    </row>
-    <row r="15" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+    </row>
+    <row r="15" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="8">
+      <c r="F15" s="8">
         <v>0.53125</v>
       </c>
-      <c r="E15" s="8">
+      <c r="G15" s="8">
         <v>0.375</v>
       </c>
-      <c r="F15" s="8">
+      <c r="H15" s="8">
         <v>9.375E-2</v>
       </c>
-      <c r="G15" s="8">
+      <c r="I15" s="8">
         <v>0.41018958333333322</v>
       </c>
-      <c r="H15" s="8">
+      <c r="J15" s="8">
         <v>0.35936562500000008</v>
       </c>
-      <c r="I15" s="8">
+      <c r="K15" s="8">
         <v>0.4375</v>
       </c>
-      <c r="J15" s="8">
+      <c r="L15" s="8">
         <v>0.33750000000000002</v>
       </c>
-      <c r="K15" s="8">
+      <c r="M15" s="8">
         <f t="shared" si="0"/>
         <v>0.38600000000000001</v>
       </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
-    </row>
-    <row r="16" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+    </row>
+    <row r="16" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="8">
+      <c r="F16" s="8">
         <v>0.3611111111111111</v>
       </c>
-      <c r="E16" s="8">
+      <c r="G16" s="8">
         <v>0.55555555555555558</v>
       </c>
-      <c r="F16" s="8">
+      <c r="H16" s="8">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G16" s="8">
+      <c r="I16" s="8">
         <v>0.42199907407407411</v>
       </c>
-      <c r="H16" s="8">
+      <c r="J16" s="8">
         <v>0.4019638888888889</v>
       </c>
-      <c r="I16" s="8">
+      <c r="K16" s="8">
         <v>0.53472222222222221</v>
       </c>
-      <c r="J16" s="8">
+      <c r="L16" s="8">
         <v>0.28333333333333333</v>
       </c>
-      <c r="K16" s="8">
+      <c r="M16" s="8">
         <f t="shared" si="0"/>
         <v>0.41099999999999998</v>
       </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
-    </row>
-    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="8">
-        <f t="shared" ref="D17:J18" si="1">IFERROR(AVERAGEIFS(D$2:D$16,$B$2:$B$16,$B17,$C$2:$C$16,$C17),"")</f>
+      <c r="F17" s="8">
+        <f t="shared" ref="F17:L18" si="1">IFERROR(AVERAGEIFS(F$2:F$16,$D$2:$D$16,$D17,$E$2:$E$16,$E17),"")</f>
         <v>0.7670428055880093</v>
       </c>
-      <c r="E17" s="8">
+      <c r="G17" s="8">
         <f t="shared" si="1"/>
         <v>0.17557117773055803</v>
       </c>
-      <c r="F17" s="8">
+      <c r="H17" s="8">
         <f t="shared" si="1"/>
         <v>5.7386016681432631E-2</v>
       </c>
-      <c r="G17" s="8">
+      <c r="I17" s="8">
         <f t="shared" si="1"/>
         <v>0.31024340707630871</v>
       </c>
-      <c r="H17" s="8">
+      <c r="J17" s="8">
         <f t="shared" si="1"/>
         <v>0.29642754827427453</v>
       </c>
-      <c r="I17" s="8">
+      <c r="K17" s="8">
         <f t="shared" si="1"/>
         <v>0.3507278658836287</v>
       </c>
-      <c r="J17" s="8">
+      <c r="L17" s="8">
         <f t="shared" si="1"/>
         <v>0.20516264610666562</v>
       </c>
-      <c r="K17" s="8">
+      <c r="M17" s="8">
         <f t="shared" si="0"/>
         <v>0.29099999999999998</v>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
-    </row>
-    <row r="18" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+    </row>
+    <row r="18" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="8">
+      <c r="F18" s="8">
         <f t="shared" si="1"/>
         <v>0.66399170274170261</v>
       </c>
-      <c r="E18" s="8">
+      <c r="G18" s="8">
         <f t="shared" si="1"/>
         <v>0.28965187590187591</v>
       </c>
-      <c r="F18" s="8">
+      <c r="H18" s="8">
         <f t="shared" si="1"/>
         <v>4.635642135642136E-2</v>
       </c>
-      <c r="G18" s="8">
+      <c r="I18" s="8">
         <f t="shared" si="1"/>
         <v>0.34667902284752278</v>
       </c>
-      <c r="H18" s="8">
+      <c r="J18" s="8">
         <f t="shared" si="1"/>
         <v>0.31787493632756136</v>
       </c>
-      <c r="I18" s="8">
+      <c r="K18" s="8">
         <f t="shared" si="1"/>
         <v>0.42526470057720062</v>
       </c>
-      <c r="J18" s="8">
+      <c r="L18" s="8">
         <f t="shared" si="1"/>
         <v>0.31431024531024526</v>
       </c>
-      <c r="K18" s="8">
+      <c r="M18" s="8">
         <f t="shared" si="0"/>
         <v>0.35099999999999998</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="K2 K3:K18" formulaRange="1"/>
+    <ignoredError sqref="M2 M3:M18" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7389,4 +7608,3184 @@
     <ignoredError sqref="J2:J18" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54D2E6-D3E1-4CCD-A700-1303E31935A9}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.80408163265306132</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0.73469387755102045</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M2" s="15">
+        <v>0.88436530612244912</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0.81318571428571418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.5674688888888888</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0.65926666666666678</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="N3" s="15">
+        <v>0.60313111111111128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H4" s="15">
+        <v>6.25E-2</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.51282708333333316</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0.63195208333333341</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0.34166666666666662</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="N4" s="15">
+        <v>0.57228749999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.46913580246913578</v>
+      </c>
+      <c r="H5" s="15">
+        <v>2.4691358024691357E-2</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0.44664691358024688</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0.38271234567901224</v>
+      </c>
+      <c r="K5" s="15">
+        <v>0.55556419753086439</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0.31790123456790126</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0.37036543209876532</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0.41463703703703692</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="H6" s="15">
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0.35164693877551018</v>
+      </c>
+      <c r="J6" s="15">
+        <v>0.70408163265306134</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0.28571428571428575</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0.50510204081632648</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0.46216326530612245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.703125</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.296875</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0.36433125</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.33158437499999999</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0.359375</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0.32031093749999989</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0.34389999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.20370370370370369</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.56166084656084658</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.57407407407407407</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.58642407407407415</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.66203703703703709</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0.73148148148148151</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0.59564259259259256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.22950819672131148</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.39344262295081966</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.37704918032786883</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0.48794918032786905</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.57650245901639341</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0.31147540983606559</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0.63934426229508201</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0.68032786885245899</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0.53711147540983606</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G10" s="15">
+        <v>0.54285714285714282</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.17142857142857143</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0.39115553571428568</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.38214285714285717</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0.56785714285714284</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0.6753985714285714</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0.46339714285714295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.17307692307692307</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.36538461538461536</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0.50333830128205148</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0.56923076923076921</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0.69872788461538482</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0.53526153846153857</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0.453125</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0.53565576923076941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.43103448275862066</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.36206896551724138</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0.45852241379310343</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.35991379310344823</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0.54885603448275877</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0.44181034482758619</v>
+      </c>
+      <c r="N12" s="15">
+        <v>0.45297068965517229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.27710843373493976</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0.40963855421686746</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0.31325301204819278</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0.54217068273092373</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.45180542168674698</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.46586325301204817</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0.57028192771084341</v>
+      </c>
+      <c r="N13" s="15">
+        <v>0.5172674698795181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="15">
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0.46296296296296297</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0.74814814814814812</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.75925925925925919</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.71296296296296291</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0.70372037037037061</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0.75516851851851829</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="H15" s="15">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0.49206000000000005</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0.77777777777777768</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0.54074222222222201</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="N15" s="15">
+        <v>0.55323111111111101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0.33870967741935482</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0.56451612903225812</v>
+      </c>
+      <c r="H16" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0.47953064516129035</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.63441290322580657</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0.62096774193548387</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0.3612903225806452</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0.66935483870967749</v>
+      </c>
+      <c r="N16" s="15">
+        <v>0.55311290322580631</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.38805970149253732</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0.55223880597014929</v>
+      </c>
+      <c r="H17" s="15">
+        <v>5.9701492537313432E-2</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0.52344925373134332</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0.46268059701492542</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0.59204925373134332</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0.30970149253731344</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0.56716417910447769</v>
+      </c>
+      <c r="N17" s="15">
+        <v>0.49101343283582083</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0.46314374999999991</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0.55729166666666663</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0.31770833333333331</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0.1875</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0.5859375</v>
+      </c>
+      <c r="N18" s="15">
+        <v>0.4223229166666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0.45680999999999977</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.47962499999999997</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0.50277500000000008</v>
+      </c>
+      <c r="N19" s="15">
+        <v>0.45980666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.58695652173913049</v>
+      </c>
+      <c r="I20" s="15">
+        <v>0.60874720496894386</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.45652173913043476</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0.69565434782608704</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0.61956521739130432</v>
+      </c>
+      <c r="M20" s="15">
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0.61596956521739121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0.32142857142857145</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0.43941862244897967</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0.52455357142857151</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="M21" s="15">
+        <v>0.63392857142857151</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0.48342321428571433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0.33269192307692314</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.34423076923076917</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0.56153846153846154</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0.58632615384615383</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0.39743589743589747</v>
+      </c>
+      <c r="N22" s="15">
+        <v>0.41245999999999972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.27692307692307694</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0.26153846153846155</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0.4327589743589742</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.48</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.61538846153846161</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0.49487615384615391</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0.52884615384615385</v>
+      </c>
+      <c r="N23" s="15">
+        <v>0.48882923076923068</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.41891891891891891</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0.43243243243243246</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0.14864864864864866</v>
+      </c>
+      <c r="I24" s="15">
+        <v>0.45975810810810808</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.33614864864864863</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.51239256756756768</v>
+      </c>
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0.42539324324324318</v>
+      </c>
+      <c r="N24" s="15">
+        <v>0.43634324324324325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.19178082191780821</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0.46575342465753422</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0.34246575342465752</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0.55479497716894977</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0.54452191780821912</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0.51598082191780814</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0.54490091324200907</v>
+      </c>
+      <c r="N25" s="15">
+        <v>0.54200821917808217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.13414634146341464</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0.52439024390243905</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0.34146341463414637</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0.63048780487804879</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.65243902439024393</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.60365853658536583</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0.68293658536585378</v>
+      </c>
+      <c r="N26" s="15">
+        <v>0.65779512195121925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0.58163265306122447</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0.31632653061224492</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0.70954795918367364</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.75510204081632648</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.81632653061224492</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0.5782326530612244</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0.60714285714285721</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0.69327142857142843</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.14166666666666666</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.64968250000000016</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0.73611583333333341</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="L28" s="15">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="M28" s="15">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="N28" s="15">
+        <v>0.69382333333333379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="15">
+        <v>0.33613445378151263</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="H29" s="15">
+        <v>9.2436974789915971E-2</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0.53391092436974796</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0.42016638655462191</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0.58823781512605045</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0.49019411764705878</v>
+      </c>
+      <c r="N29" s="15">
+        <v>0.47792521008403355</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="15">
+        <v>9.0090090090090086E-2</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0.63963963963963966</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="I30" s="15">
+        <v>0.60845945945945934</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0.83108108108108114</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0.71846846846846846</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0.55630630630630629</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0.60923423423423417</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0.66470540540540579</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="15">
+        <v>0.56302521008403361</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0.36974789915966388</v>
+      </c>
+      <c r="H31" s="15">
+        <v>6.7226890756302518E-2</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0.38462941176470578</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0.45844285714285699</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0.40336134453781514</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0.39775966386554612</v>
+      </c>
+      <c r="N31" s="15">
+        <v>0.41104789915966372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.24324324324324326</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0.28378378378378377</v>
+      </c>
+      <c r="H32" s="15">
+        <v>0.47297297297297297</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0.53684034749034737</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0.54054054054054057</v>
+      </c>
+      <c r="K32" s="15">
+        <v>0.5360364864864865</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.6283783783783784</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0.69594594594594594</v>
+      </c>
+      <c r="N32" s="15">
+        <v>0.56560135135135114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="15">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="I33" s="15">
+        <v>0.58076309523809566</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0.67144062500000001</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M33" s="15">
+        <v>0.78645833333333326</v>
+      </c>
+      <c r="N33" s="15">
+        <v>0.6467197916666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.390625</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0.40625</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0.203125</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0.40278593749999997</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0.3466796875</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0.56640625</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0.56423776041666618</v>
+      </c>
+      <c r="M34" s="15">
+        <v>0.45963541666666663</v>
+      </c>
+      <c r="N34" s="15">
+        <v>0.45111718749999979</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="15">
+        <v>7.03125E-2</v>
+      </c>
+      <c r="G35" s="15">
+        <v>0.203125</v>
+      </c>
+      <c r="H35" s="15">
+        <v>0.7265625</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0.67849518229166661</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0.69687500000000002</v>
+      </c>
+      <c r="K35" s="15">
+        <v>0.77865234374999914</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0.66536875000000006</v>
+      </c>
+      <c r="M35" s="15">
+        <v>0.6845703125</v>
+      </c>
+      <c r="N35" s="15">
+        <v>0.69423203124999988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0.18548387096774194</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0.45967741935483869</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0.54448763440860215</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0.49899193548387094</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0.72580766129032237</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15">
+        <v>0.56955685483870966</v>
+      </c>
+      <c r="N36" s="15">
+        <v>0.5802459677419356</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0.19379844961240311</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="H37" s="15">
+        <v>0.4573643410852713</v>
+      </c>
+      <c r="I37" s="15">
+        <v>0.61050826873385</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0.51808604651162793</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0.53165542635658913</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15">
+        <v>0.59538888888888908</v>
+      </c>
+      <c r="N37" s="15">
+        <v>0.57171782945736438</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8147AE5B-C20B-4DEF-A7F6-B50B97C6DCC0}">
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.12</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.42</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.46</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.64833199999999991</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0.54</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0.62944600000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.38</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0.75466399999999989</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0.7018859999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="15">
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.32203389830508472</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.61016440677966088</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0.6451271186440678</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0.64406779661016955</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0.63311186440677969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.23655913978494625</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.63440860215053763</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0.58243655913978498</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0.52625698924731201</v>
+      </c>
+      <c r="K5" s="15">
+        <v>0.40591397849462368</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0.50486989247311842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.22033898305084745</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.50847457627118642</v>
+      </c>
+      <c r="H6" s="15">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0.70847457627118648</v>
+      </c>
+      <c r="J6" s="15">
+        <v>0.56645593220338974</v>
+      </c>
+      <c r="K6" s="15">
+        <v>0.42584745762711862</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0.56692881355932234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.21621621621621623</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.68918918918918914</v>
+      </c>
+      <c r="H7" s="15">
+        <v>9.45945945945946E-2</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0.66891891891891886</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.56543108108108098</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0.40829594594594587</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0.54754459459459459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.29268292682926828</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.31707317073170732</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.68699268292682936</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.56585365853658542</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.40243902439024387</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.55176097560975623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="I9" s="15">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0.6153883333333332</v>
+      </c>
+      <c r="K9" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0.48179666666666665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="G10" s="15">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.80645161290322576</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0.84676935483870963</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.72473870967741949</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0.70125483870967753</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.62666666666666671</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0.5964506666666668</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0.6310399999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.26168224299065418</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.44859813084112149</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0.28971962616822428</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0.52336448598130847</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.4972943925233646</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0.51635514018691586</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0.5123392523364485</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.17741935483870969</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0.40322580645161288</v>
+      </c>
+      <c r="H13" s="15">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0.56451612903225812</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.51867419354838729</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.59193548387096773</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0.55837258064516138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.1875</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0.74687499999999996</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.54874999999999996</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.44270625000000008</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0.57944249999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="15">
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0.79215686274509811</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.7058843137254901</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0.57352941176470584</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0.69052352941176465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="15">
+        <v>8.1632653061224483E-2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0.65306122448979587</v>
+      </c>
+      <c r="H16" s="15">
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0.67346938775510212</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.68571836734693892</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0.18877551020408162</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0.51598775510204087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.125</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0.5892857142857143</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0.58928214285714275</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0.63392857142857151</v>
+      </c>
+      <c r="K17" s="15">
+        <v>0.41517857142857145</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0.54613035714285718</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.16981132075471697</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0.60377358490566035</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0.6981094339622641</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0.61820377358490541</v>
+      </c>
+      <c r="K18" s="15">
+        <v>0.44339622641509435</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0.58657735849056603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.21818181818181817</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0.58181818181818179</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0.67636363636363639</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.51579818181818204</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0.38636363636363635</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0.52617272727272735</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.26865671641791045</v>
+      </c>
+      <c r="G20" s="15">
+        <v>0.62686567164179108</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="I20" s="15">
+        <v>0.56343283582089554</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0.57816119402985078</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0.40831492537313435</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0.51663880597014922</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0.65</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="K21" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0.65833499999999989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0.66530612244897958</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.67739591836734681</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0.33673469387755106</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0.55981428571428582</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0.79737843137254882</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.7058803921568626</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0.62526078431372545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.25423728813559321</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0.30508474576271188</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0.44067796610169491</v>
+      </c>
+      <c r="I24" s="15">
+        <v>0.71398305084745761</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.60565084745762698</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.3135593220338983</v>
+      </c>
+      <c r="L24" s="15">
+        <v>0.54439830508474574</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.28169014084507044</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0.40845070422535212</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0.30985915492957744</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0.59859154929577463</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0.52557464788732366</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0.42957746478873238</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0.51792112676056345</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.39344262295081966</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0.26229508196721313</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0.34426229508196721</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0.56147540983606559</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.5125065573770492</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.44098360655737706</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0.50499344262295087</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.13580246913580246</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0.34567901234567899</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0.51851851851851849</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.41357777777777771</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0.5971209876543212</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.28048780487804881</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0.3048780487804878</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0.41463414634146339</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.67804878048780493</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0.55996219512195122</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.52134146341463417</v>
+      </c>
+      <c r="L28" s="15">
+        <v>0.58644390243902422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1.0309278350515464E-2</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0.51546391752577314</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0.47422680412371132</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0.72989690721649481</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0.76151443298969068</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0.70103092783505161</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0.7308154639175255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="15">
+        <v>0.12844036697247707</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0.47706422018348627</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0.39449541284403672</v>
+      </c>
+      <c r="I30" s="15">
+        <v>0.64067247706422026</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0.64793577981651385</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0.71330275229357798</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0.66730550458715587</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="15">
+        <v>4.807692307692308E-2</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0.70192307692307687</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="I31" s="15">
+        <v>0.69390480769230767</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0.64084038461538451</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0.64903846153846156</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0.66125865384615423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.11214953271028037</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0.52336448598130836</v>
+      </c>
+      <c r="H32" s="15">
+        <v>0.3644859813084112</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0.71962616822429903</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0.63501962616822438</v>
+      </c>
+      <c r="K32" s="15">
+        <v>0.5490654205607477</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.63457289719626153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="15">
+        <v>0.1484375</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0.734375</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0.1171875</v>
+      </c>
+      <c r="I33" s="15">
+        <v>0.75390625</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0.61471718750000004</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0.50055859375</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0.62306249999999974</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.35802469135802467</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0.2839506172839506</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0.35802469135802467</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0.66460740740740731</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0.57901234567901239</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0.3271604938271605</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0.52360000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="15">
+        <v>0.32876712328767121</v>
+      </c>
+      <c r="G35" s="15">
+        <v>0.26027397260273971</v>
+      </c>
+      <c r="H35" s="15">
+        <v>0.41095890410958902</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0.57808219178082187</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0.63857397260273929</v>
+      </c>
+      <c r="K35" s="15">
+        <v>0.36986301369863012</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0.52884109589041084</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="15">
+        <v>1.0101010101010102E-2</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.14141414141414141</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0.84848484848484851</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0.88046767676767668</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0.77441414141414144</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0.6767676767676768</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0.77722323232323265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.2076923076923077</v>
+      </c>
+      <c r="H37" s="15">
+        <v>0.63846153846153841</v>
+      </c>
+      <c r="I37" s="15">
+        <v>0.75096153846153835</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0.6215376923076924</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0.65192307692307694</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0.67480692307692325</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="15">
+        <v>7.5471698113207544E-2</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="H38" s="15">
+        <v>0.68867924528301883</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0.72169811320754718</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0.70257830188679238</v>
+      </c>
+      <c r="K38" s="15">
+        <v>0.68985849056603765</v>
+      </c>
+      <c r="L38" s="15">
+        <v>0.70471226415094324</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="15">
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0.37606837606837606</v>
+      </c>
+      <c r="H39" s="15">
+        <v>0.36752136752136755</v>
+      </c>
+      <c r="I39" s="15">
+        <v>0.55982905982905984</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0.48133504273504263</v>
+      </c>
+      <c r="K39" s="15">
+        <v>0.51452991452991459</v>
+      </c>
+      <c r="L39" s="15">
+        <v>0.51856666666666673</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="15">
+        <v>0.28440366972477066</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0.34862385321100919</v>
+      </c>
+      <c r="H40" s="15">
+        <v>0.3669724770642202</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0.65137614678899081</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0.51376146788990829</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0.37156055045871567</v>
+      </c>
+      <c r="L40" s="15">
+        <v>0.5122321100917433</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CEDD422-95CF-44C7-A9B7-A6394C842A41}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86B53E65-A5CD-445A-867F-09955D746A05}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="59">
   <si>
     <t>CURSO</t>
   </si>
@@ -214,6 +214,12 @@
   <si>
     <t>2BÁSICO</t>
   </si>
+  <si>
+    <t>MEDIA LA</t>
+  </si>
+  <si>
+    <t>MEDIA SF</t>
+  </si>
 </sst>
 </file>
 
@@ -224,7 +230,7 @@
     <numFmt numFmtId="165" formatCode="#,##0%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +274,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -324,7 +336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -432,12 +444,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -537,12 +608,979 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0.0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -555,8 +1593,47 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{603625AB-3424-4720-B64C-3A94669BB298}" name="Tabla2" displayName="Tabla2" ref="A1:N41" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:N41" xr:uid="{603625AB-3424-4720-B64C-3A94669BB298}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{C4951A27-4154-41B9-B8D4-A85237FF27BF}" name="PERÍODO" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{5E8E4C53-105C-4F0F-B81B-43DF12C5AD0C}" name="UNIDAD ACADÉMICA" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{1622C96A-86CF-4A32-88C0-A8FD0D98D6A4}" name="ASIGNATURA" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{AAE76B90-D559-4C6D-BCE8-2CB5914A2688}" name="ETAPA" dataDxfId="11" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{B27D401D-C4DB-4F5A-907B-A46E26DCD2EB}" name="NIVEL" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{82381162-CBF8-4ECF-B3AF-DA6791C58B9F}" name="NIVEL I" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{B10D23DF-EC5A-4F8C-AF44-37E67CAA187A}" name="NIVEL II" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{65D81586-5C35-48A1-9AC1-4470C0B6F64C}" name="NIVEL III" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{54F6FC8D-DFEF-4061-93FF-C58C6CAA5482}" name="num" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{A588398E-D9E2-47E2-A40D-A54D5A1F8777}" name="alg" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{24694D93-E6C0-4608-803B-1BBFBA44AFB1}" name="geo" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{28D83C33-2DC3-47CD-9ADC-F1FF73A0D836}" name="dat" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{2FD8D12D-E6C6-480D-9CEF-EE7BE8A525CC}" name="med" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{40066EBD-274C-4BC8-B1C6-81AF6378E2A8}" name="prom_mat" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BBE7D88-08B6-4227-B44B-6F2AACDCA85A}" name="Tabla1" displayName="Tabla1" ref="A1:L44" totalsRowShown="0" headerRowDxfId="21" dataDxfId="22" dataCellStyle="Porcentaje">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{BFABC6FB-038F-4877-A79C-66D905599850}" name="PERÍODO" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{2A4B2E8A-F289-455C-8AF2-142A5B5039FA}" name="UNIDAD ACADÉMICA" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{75021AED-3042-4D7B-A073-F60F1DCB4EF4}" name="ASIGNATURA" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{AD981768-D01C-4F19-A096-A7441E4E5255}" name="ETAPA" dataDxfId="20" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{C59B8166-AA39-4643-8D4D-56C399243BF4}" name="NIVEL" dataDxfId="18" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{D2F2AB2A-0FB6-4DE1-963A-D22995224D52}" name="NIVEL I" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{0D50C56D-C38A-4557-8265-DC6576552F9D}" name="NIVEL II" dataDxfId="28" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{001A79ED-9900-4053-90F8-0D8D7517B7EA}" name="NIVEL III" dataDxfId="27" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{40675EC1-4EDC-4294-ADD7-CD999FEEEE37}" name="loc" dataDxfId="26" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{07846A22-0AB6-49E3-8E77-E4DF29BC232E}" name="int" dataDxfId="25" dataCellStyle="Porcentaje"/>
+    <tableColumn id="11" xr3:uid="{824A9A32-EBF9-4D91-BCF1-21F5FB910191}" name="ref" dataDxfId="24" dataCellStyle="Porcentaje"/>
+    <tableColumn id="12" xr3:uid="{2FAFF1D1-ACFC-409D-980E-C4DD4A1272CF}" name="prom_len" dataDxfId="23" dataCellStyle="Porcentaje"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7612,1657 +8689,1833 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54D2E6-D3E1-4CCD-A700-1303E31935A9}">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="12.85546875" customWidth="1"/>
+    <col min="5" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="14" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="49" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="50">
         <v>2026</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="40">
         <v>0</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="40">
         <v>0.2857142857142857</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="40">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="40">
         <v>0.80408163265306132</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="40">
         <v>0.7857142857142857</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="40">
         <v>0.73469387755102045</v>
       </c>
-      <c r="L2" s="15">
+      <c r="L2" s="40">
         <v>0.8571428571428571</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="40">
         <v>0.88436530612244912</v>
       </c>
-      <c r="N2" s="15">
+      <c r="N2" s="51">
         <v>0.81318571428571418</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="50">
         <v>2026</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="40">
         <v>0.26666666666666666</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="40">
         <v>0.53333333333333333</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="40">
         <v>0.2</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="40">
         <v>0.5674688888888888</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="40">
         <v>0.52222222222222225</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="40">
         <v>0.74444444444444446</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="40">
         <v>0.65926666666666678</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="40">
         <v>0.52222222222222225</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="51">
         <v>0.60313111111111128</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="50">
         <v>2026</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="40">
         <v>0.29166666666666669</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="40">
         <v>0.64583333333333337</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="40">
         <v>6.25E-2</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="40">
         <v>0.51282708333333316</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="40">
         <v>0.63195208333333341</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="40">
         <v>0.75</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="40">
         <v>0.34166666666666662</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="40">
         <v>0.625</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="51">
         <v>0.57228749999999995</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="50">
         <v>2026</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="40">
         <v>0.50617283950617287</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="40">
         <v>0.46913580246913578</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="40">
         <v>2.4691358024691357E-2</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="40">
         <v>0.44664691358024688</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="40">
         <v>0.38271234567901224</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="40">
         <v>0.55556419753086439</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="40">
         <v>0.31790123456790126</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="40">
         <v>0.37036543209876532</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="51">
         <v>0.41463703703703692</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="50">
         <v>2026</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="40">
         <v>0.48979591836734693</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="40">
         <v>0.48979591836734693</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="40">
         <v>2.0408163265306121E-2</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="40">
         <v>0.35164693877551018</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="40">
         <v>0.70408163265306134</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="40">
         <v>0.4642857142857143</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="40">
         <v>0.28571428571428575</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="40">
         <v>0.50510204081632648</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="51">
         <v>0.46216326530612245</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="50">
         <v>2026</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="40">
         <v>0.703125</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="40">
         <v>0.296875</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="40">
         <v>0</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="40">
         <v>0.36433125</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="40">
         <v>0.33158437499999999</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="40">
         <v>0.359375</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="40">
         <v>0</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="40">
         <v>0.32031093749999989</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="51">
         <v>0.34389999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="50">
         <v>2026</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="40">
         <v>0.20370370370370369</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="40">
         <v>0.29629629629629628</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="40">
         <v>0.5</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="40">
         <v>0.56166084656084658</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="40">
         <v>0.57407407407407407</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="40">
         <v>0.58642407407407415</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="40">
         <v>0.66203703703703709</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="40">
         <v>0.73148148148148151</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="51">
         <v>0.59564259259259256</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="50">
         <v>2026</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="40">
         <v>0.22950819672131148</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="40">
         <v>0.39344262295081966</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="40">
         <v>0.37704918032786883</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="40">
         <v>0.48794918032786905</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="40">
         <v>0.57650245901639341</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="40">
         <v>0.31147540983606559</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="40">
         <v>0.63934426229508201</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="40">
         <v>0.68032786885245899</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="51">
         <v>0.53711147540983606</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="50">
         <v>2026</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="40">
         <v>0.2857142857142857</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="40">
         <v>0.54285714285714282</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="40">
         <v>0.17142857142857143</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="40">
         <v>0.39115553571428568</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="40">
         <v>0.38214285714285717</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="40">
         <v>0.56785714285714284</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="40">
         <v>0.6753985714285714</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="40">
         <v>0.42857142857142855</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="51">
         <v>0.46339714285714295</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="50">
         <v>2026</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="40">
         <v>0.17307692307692307</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="40">
         <v>0.46153846153846156</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="40">
         <v>0.36538461538461536</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="40">
         <v>0.50333830128205148</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="40">
         <v>0.56923076923076921</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="40">
         <v>0.69872788461538482</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="40">
         <v>0.53526153846153857</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="40">
         <v>0.453125</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="51">
         <v>0.53565576923076941</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="50">
         <v>2026</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="40">
         <v>0.43103448275862066</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="40">
         <v>0.36206896551724138</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="40">
         <v>0.20689655172413793</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="40">
         <v>0.45852241379310343</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="40">
         <v>0.35991379310344823</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="40">
         <v>0.54885603448275877</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="40">
         <v>0</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="40">
         <v>0.44181034482758619</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="51">
         <v>0.45297068965517229</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="50">
         <v>2026</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="40">
         <v>0.27710843373493976</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="40">
         <v>0.40963855421686746</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="40">
         <v>0.31325301204819278</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="40">
         <v>0.54217068273092373</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="40">
         <v>0.45180542168674698</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="40">
         <v>0.46586325301204817</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="40">
         <v>0</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="40">
         <v>0.57028192771084341</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="51">
         <v>0.5172674698795181</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="50">
         <v>2026</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="40">
         <v>3.7037037037037035E-2</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="40">
         <v>0.46296296296296297</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="40">
         <v>0.5</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="40">
         <v>0.74814814814814812</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="40">
         <v>0.75925925925925919</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="40">
         <v>0.71296296296296291</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="40">
         <v>0.85185185185185186</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="40">
         <v>0.70372037037037061</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="51">
         <v>0.75516851851851829</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="50">
         <v>2026</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="40">
         <v>0.37777777777777777</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="40">
         <v>0.55555555555555558</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="40">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="40">
         <v>0.49206000000000005</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="40">
         <v>0.4777777777777778</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="40">
         <v>0.77777777777777768</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="40">
         <v>0.54074222222222201</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="40">
         <v>0.4777777777777778</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="51">
         <v>0.55323111111111101</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="50">
         <v>2026</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="40">
         <v>0.33870967741935482</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="40">
         <v>0.56451612903225812</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="40">
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="40">
         <v>0.47953064516129035</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="40">
         <v>0.63441290322580657</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="40">
         <v>0.62096774193548387</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="40">
         <v>0.3612903225806452</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="40">
         <v>0.66935483870967749</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="51">
         <v>0.55311290322580631</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="50">
         <v>2026</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="40">
         <v>0.38805970149253732</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="40">
         <v>0.55223880597014929</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="40">
         <v>5.9701492537313432E-2</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="40">
         <v>0.52344925373134332</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="40">
         <v>0.46268059701492542</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="40">
         <v>0.59204925373134332</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="40">
         <v>0.30970149253731344</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="40">
         <v>0.56716417910447769</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="51">
         <v>0.49101343283582083</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="50">
         <v>2026</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="40">
         <v>0.5625</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="40">
         <v>0.4375</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="40">
         <v>0</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="40">
         <v>0.46314374999999991</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="40">
         <v>0.55729166666666663</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="40">
         <v>0.31770833333333331</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="40">
         <v>0.1875</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="40">
         <v>0.5859375</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="51">
         <v>0.4223229166666666</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="50">
         <v>2026</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="40">
         <v>0.35</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="40">
         <v>0.6</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="40">
         <v>0.05</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="40">
         <v>0.45680999999999977</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="40">
         <v>0.47962499999999997</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="40">
         <v>0.4</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="40">
         <v>0</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="40">
         <v>0.50277500000000008</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="51">
         <v>0.45980666666666664</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="50">
         <v>2026</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="40">
         <v>0.17391304347826086</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="40">
         <v>0.2391304347826087</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="40">
         <v>0.58695652173913049</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="40">
         <v>0.60874720496894386</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="40">
         <v>0.45652173913043476</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="40">
         <v>0.69565434782608704</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="40">
         <v>0.61956521739130432</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="40">
         <v>0.73913043478260876</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="51">
         <v>0.61596956521739121</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="50">
         <v>2026</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="40">
         <v>0.3392857142857143</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="40">
         <v>0.32142857142857145</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="40">
         <v>0.3392857142857143</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="40">
         <v>0.43941862244897967</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="40">
         <v>0.52455357142857151</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="40">
         <v>0.25</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="40">
         <v>0.5625</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="40">
         <v>0.63392857142857151</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="51">
         <v>0.48342321428571433</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="50">
         <v>2026</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="40">
         <v>0.44615384615384618</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="40">
         <v>0.44615384615384618</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="40">
         <v>0.1076923076923077</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="40">
         <v>0.33269192307692314</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="40">
         <v>0.34423076923076917</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="40">
         <v>0.56153846153846154</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="40">
         <v>0.58632615384615383</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="40">
         <v>0.39743589743589747</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="51">
         <v>0.41245999999999972</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="50">
         <v>2026</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="40">
         <v>0.27692307692307694</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="40">
         <v>0.46153846153846156</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="40">
         <v>0.26153846153846155</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="40">
         <v>0.4327589743589742</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="40">
         <v>0.48</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="40">
         <v>0.61538846153846161</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="40">
         <v>0.49487615384615391</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="40">
         <v>0.52884615384615385</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="51">
         <v>0.48882923076923068</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="50">
         <v>2026</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="40">
         <v>0.41891891891891891</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="40">
         <v>0.43243243243243246</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="40">
         <v>0.14864864864864866</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="40">
         <v>0.45975810810810808</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="40">
         <v>0.33614864864864863</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="40">
         <v>0.51239256756756768</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="40">
         <v>0</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="40">
         <v>0.42539324324324318</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="51">
         <v>0.43634324324324325</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="50">
         <v>2026</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="40">
         <v>0.19178082191780821</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="40">
         <v>0.46575342465753422</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="40">
         <v>0.34246575342465752</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="40">
         <v>0.55479497716894977</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="40">
         <v>0.54452191780821912</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="40">
         <v>0.51598082191780814</v>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="40">
         <v>0</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="40">
         <v>0.54490091324200907</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="51">
         <v>0.54200821917808217</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="50">
         <v>2026</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="40">
         <v>0.13414634146341464</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="40">
         <v>0.52439024390243905</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="40">
         <v>0.34146341463414637</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="40">
         <v>0.63048780487804879</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="40">
         <v>0.65243902439024393</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="40">
         <v>0.60365853658536583</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="40">
         <v>0.71951219512195119</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="40">
         <v>0.68293658536585378</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="51">
         <v>0.65779512195121925</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="50">
         <v>2026</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="40">
         <v>0.10204081632653061</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="40">
         <v>0.58163265306122447</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="40">
         <v>0.31632653061224492</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="40">
         <v>0.70954795918367364</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="40">
         <v>0.75510204081632648</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="40">
         <v>0.81632653061224492</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="40">
         <v>0.5782326530612244</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="40">
         <v>0.60714285714285721</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="51">
         <v>0.69327142857142843</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="50">
         <v>2026</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="40">
         <v>0.14166666666666666</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="40">
         <v>0.49166666666666664</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="40">
         <v>0.36666666666666664</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="40">
         <v>0.64968250000000016</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="40">
         <v>0.73611583333333341</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="40">
         <v>0.77500000000000002</v>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="40">
         <v>0.56666666666666665</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="40">
         <v>0.7416666666666667</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="51">
         <v>0.69382333333333379</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="50">
         <v>2026</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="40">
         <v>0.33613445378151263</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="40">
         <v>0.5714285714285714</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="40">
         <v>9.2436974789915971E-2</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="40">
         <v>0.53391092436974796</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="40">
         <v>0.42016638655462191</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="40">
         <v>0.58823781512605045</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="40">
         <v>0.35714285714285715</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="40">
         <v>0.49019411764705878</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="51">
         <v>0.47792521008403355</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="50">
         <v>2026</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="40">
         <v>9.0090090090090086E-2</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="40">
         <v>0.63963963963963966</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="40">
         <v>0.27027027027027029</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="40">
         <v>0.60845945945945934</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="40">
         <v>0.83108108108108114</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="40">
         <v>0.71846846846846846</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="40">
         <v>0.55630630630630629</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="40">
         <v>0.60923423423423417</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="51">
         <v>0.66470540540540579</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="50">
         <v>2026</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="40">
         <v>0.56302521008403361</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="40">
         <v>0.36974789915966388</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="40">
         <v>6.7226890756302518E-2</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="40">
         <v>0.38462941176470578</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="40">
         <v>0.45844285714285699</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="40">
         <v>0.40336134453781514</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="40">
         <v>0</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="40">
         <v>0.39775966386554612</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="51">
         <v>0.41104789915966372</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="50">
         <v>2026</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="40">
         <v>0.24324324324324326</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="40">
         <v>0.28378378378378377</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="40">
         <v>0.47297297297297297</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="40">
         <v>0.53684034749034737</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="40">
         <v>0.54054054054054057</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="40">
         <v>0.5360364864864865</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="40">
         <v>0.6283783783783784</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="40">
         <v>0.69594594594594594</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="51">
         <v>0.56560135135135114</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="50">
         <v>2026</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="40">
         <v>6.25E-2</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="40">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="40">
         <v>0.60416666666666663</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="40">
         <v>0.58076309523809566</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="40">
         <v>0.67144062500000001</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="40">
         <v>0.57291666666666663</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="40">
         <v>0.75</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="40">
         <v>0.78645833333333326</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="51">
         <v>0.6467197916666666</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="50">
         <v>2026</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="40">
         <v>0.390625</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="40">
         <v>0.40625</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="40">
         <v>0.203125</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="40">
         <v>0.40278593749999997</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="40">
         <v>0.3466796875</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="40">
         <v>0.56640625</v>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="40">
         <v>0.56423776041666618</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34" s="40">
         <v>0.45963541666666663</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34" s="51">
         <v>0.45111718749999979</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35" s="50">
         <v>2026</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="40">
         <v>7.03125E-2</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="40">
         <v>0.203125</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="40">
         <v>0.7265625</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="40">
         <v>0.67849518229166661</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="40">
         <v>0.69687500000000002</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="40">
         <v>0.77865234374999914</v>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="40">
         <v>0.66536875000000006</v>
       </c>
-      <c r="M35" s="15">
+      <c r="M35" s="40">
         <v>0.6845703125</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35" s="51">
         <v>0.69423203124999988</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36" s="50">
         <v>2026</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="40">
         <v>0.18548387096774194</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="40">
         <v>0.35483870967741937</v>
       </c>
-      <c r="H36" s="15">
+      <c r="H36" s="40">
         <v>0.45967741935483869</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="40">
         <v>0.54448763440860215</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="40">
         <v>0.49899193548387094</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="40">
         <v>0.72580766129032237</v>
       </c>
-      <c r="L36" s="15">
+      <c r="L36" s="40">
         <v>0</v>
       </c>
-      <c r="M36" s="15">
+      <c r="M36" s="40">
         <v>0.56955685483870966</v>
       </c>
-      <c r="N36" s="15">
+      <c r="N36" s="51">
         <v>0.5802459677419356</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="50">
         <v>2026</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="40">
         <v>0.19379844961240311</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="40">
         <v>0.34883720930232559</v>
       </c>
-      <c r="H37" s="15">
+      <c r="H37" s="40">
         <v>0.4573643410852713</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="40">
         <v>0.61050826873385</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="40">
         <v>0.51808604651162793</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="40">
         <v>0.53165542635658913</v>
       </c>
-      <c r="L37" s="15">
+      <c r="L37" s="40">
         <v>0</v>
       </c>
-      <c r="M37" s="15">
+      <c r="M37" s="40">
         <v>0.59538888888888908</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37" s="40">
         <v>0.57171782945736438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="50">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="40">
+        <v>0.6301186369368188</v>
+      </c>
+      <c r="G38" s="40">
+        <v>0.28768882518882521</v>
+      </c>
+      <c r="H38" s="40">
+        <v>8.2192537874356042E-2</v>
+      </c>
+      <c r="I38" s="40">
+        <v>0.38680809132775046</v>
+      </c>
+      <c r="J38" s="40">
+        <v>0.37389538298629205</v>
+      </c>
+      <c r="K38" s="40">
+        <v>0.37879495852552675</v>
+      </c>
+      <c r="L38" s="40">
+        <v>0.21198829196448515</v>
+      </c>
+      <c r="M38" s="40"/>
+      <c r="N38" s="40">
+        <v>0.33787168120101357</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="50">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="40">
+        <v>0.73620492009604921</v>
+      </c>
+      <c r="G39" s="40">
+        <v>0.21554033322178484</v>
+      </c>
+      <c r="H39" s="40">
+        <v>4.825474668216604E-2</v>
+      </c>
+      <c r="I39" s="40">
+        <v>0.33403246918234214</v>
+      </c>
+      <c r="J39" s="40">
+        <v>0.30533560177607966</v>
+      </c>
+      <c r="K39" s="40">
+        <v>0.33658782912311136</v>
+      </c>
+      <c r="L39" s="40">
+        <v>0.26125668813975267</v>
+      </c>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40">
+        <v>0.30930314705532147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="50">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="40">
+        <v>0.63721689055393171</v>
+      </c>
+      <c r="G40" s="40">
+        <v>0.21504231025226575</v>
+      </c>
+      <c r="H40" s="40">
+        <v>0.14774079919380251</v>
+      </c>
+      <c r="I40" s="40">
+        <v>0.37560324588882354</v>
+      </c>
+      <c r="J40" s="40">
+        <v>0.38080186609476968</v>
+      </c>
+      <c r="K40" s="40">
+        <v>0.38653100187711908</v>
+      </c>
+      <c r="L40" s="40">
+        <v>0.28662205622204751</v>
+      </c>
+      <c r="M40" s="40"/>
+      <c r="N40" s="40">
+        <v>0.35738954252069</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="52">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="40">
+        <v>0.7829624717555751</v>
+      </c>
+      <c r="G41" s="40">
+        <v>0.15947385548678653</v>
+      </c>
+      <c r="H41" s="40">
+        <v>5.7563672757638275E-2</v>
+      </c>
+      <c r="I41" s="40">
+        <v>0.30763713306808138</v>
+      </c>
+      <c r="J41" s="40">
+        <v>0.28555623814962178</v>
+      </c>
+      <c r="K41" s="40">
+        <v>0.31015885953924749</v>
+      </c>
+      <c r="L41" s="40">
+        <v>0.29811603546517346</v>
+      </c>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40">
+        <v>0.30036706655553103</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8147AE5B-C20B-4DEF-A7F6-B50B97C6DCC0}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9316,7 +10569,7 @@
       <c r="D2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F2" s="15">
@@ -9354,7 +10607,7 @@
       <c r="D3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="15">
@@ -9392,7 +10645,7 @@
       <c r="D4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="15">
@@ -9430,7 +10683,7 @@
       <c r="D5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="15">
@@ -9468,7 +10721,7 @@
       <c r="D6" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F6" s="15">
@@ -9506,7 +10759,7 @@
       <c r="D7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="15">
@@ -9544,7 +10797,7 @@
       <c r="D8" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="37" t="s">
         <v>56</v>
       </c>
       <c r="F8" s="15">
@@ -9582,7 +10835,7 @@
       <c r="D9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F9" s="15">
@@ -9620,7 +10873,7 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="15">
@@ -9658,7 +10911,7 @@
       <c r="D11" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="15">
@@ -9696,7 +10949,7 @@
       <c r="D12" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="15">
@@ -9734,7 +10987,7 @@
       <c r="D13" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F13" s="15">
@@ -9772,7 +11025,7 @@
       <c r="D14" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F14" s="15">
@@ -9810,7 +11063,7 @@
       <c r="D15" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="15">
@@ -9848,7 +11101,7 @@
       <c r="D16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="15">
@@ -9886,7 +11139,7 @@
       <c r="D17" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="15">
@@ -9924,7 +11177,7 @@
       <c r="D18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F18" s="15">
@@ -9962,7 +11215,7 @@
       <c r="D19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="15">
@@ -10000,7 +11253,7 @@
       <c r="D20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F20" s="15">
@@ -10038,7 +11291,7 @@
       <c r="D21" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="37" t="s">
         <v>56</v>
       </c>
       <c r="F21" s="15">
@@ -10076,7 +11329,7 @@
       <c r="D22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="15">
@@ -10114,7 +11367,7 @@
       <c r="D23" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="15">
@@ -10152,7 +11405,7 @@
       <c r="D24" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="15">
@@ -10190,7 +11443,7 @@
       <c r="D25" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F25" s="15">
@@ -10228,7 +11481,7 @@
       <c r="D26" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F26" s="15">
@@ -10266,7 +11519,7 @@
       <c r="D27" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F27" s="15">
@@ -10304,7 +11557,7 @@
       <c r="D28" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F28" s="15">
@@ -10342,7 +11595,7 @@
       <c r="D29" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F29" s="15">
@@ -10380,7 +11633,7 @@
       <c r="D30" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F30" s="15">
@@ -10418,7 +11671,7 @@
       <c r="D31" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F31" s="15">
@@ -10456,7 +11709,7 @@
       <c r="D32" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F32" s="15">
@@ -10494,7 +11747,7 @@
       <c r="D33" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="37" t="s">
         <v>50</v>
       </c>
       <c r="F33" s="15">
@@ -10532,7 +11785,7 @@
       <c r="D34" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="37" t="s">
         <v>56</v>
       </c>
       <c r="F34" s="15">
@@ -10570,7 +11823,7 @@
       <c r="D35" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="37" t="s">
         <v>45</v>
       </c>
       <c r="F35" s="15">
@@ -10608,7 +11861,7 @@
       <c r="D36" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F36" s="15">
@@ -10646,7 +11899,7 @@
       <c r="D37" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F37" s="15">
@@ -10684,7 +11937,7 @@
       <c r="D38" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="37" t="s">
         <v>48</v>
       </c>
       <c r="F38" s="15">
@@ -10722,7 +11975,7 @@
       <c r="D39" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="37" t="s">
         <v>49</v>
       </c>
       <c r="F39" s="15">
@@ -10748,44 +12001,200 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="35">
         <v>2026</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="36">
         <v>0.28440366972477066</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="36">
         <v>0.34862385321100919</v>
       </c>
-      <c r="H40" s="15">
+      <c r="H40" s="36">
         <v>0.3669724770642202</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="36">
         <v>0.65137614678899081</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="36">
         <v>0.51376146788990829</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="36">
         <v>0.37156055045871567</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="36">
         <v>0.5122321100917433</v>
       </c>
     </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="39">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="40">
+        <v>0.17755561472666737</v>
+      </c>
+      <c r="G41" s="40">
+        <v>0.27969471949735109</v>
+      </c>
+      <c r="H41" s="40">
+        <v>0.54274966577598149</v>
+      </c>
+      <c r="I41" s="40">
+        <v>0.6982912355445251</v>
+      </c>
+      <c r="J41" s="40">
+        <v>0.56044774452669199</v>
+      </c>
+      <c r="K41" s="40">
+        <v>0.54416366662616666</v>
+      </c>
+      <c r="L41" s="40">
+        <v>0.60096754889912796</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="39">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="40">
+        <v>7.0494247257767179E-2</v>
+      </c>
+      <c r="G42" s="40">
+        <v>0.20187312476686289</v>
+      </c>
+      <c r="H42" s="40">
+        <v>0.72763262797536987</v>
+      </c>
+      <c r="I42" s="40">
+        <v>0.82330834453371238</v>
+      </c>
+      <c r="J42" s="40">
+        <v>0.6663734712923769</v>
+      </c>
+      <c r="K42" s="40">
+        <v>0.60223371900628186</v>
+      </c>
+      <c r="L42" s="40">
+        <v>0.69730517827745719</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="39">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0.33237909044360664</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0.36456733230926774</v>
+      </c>
+      <c r="H43" s="15">
+        <v>0.30305357724712562</v>
+      </c>
+      <c r="I43" s="15">
+        <v>0.57466368756691344</v>
+      </c>
+      <c r="J43" s="15">
+        <v>0.48212423776939906</v>
+      </c>
+      <c r="K43" s="15">
+        <v>0.43988046944095327</v>
+      </c>
+      <c r="L43" s="15">
+        <v>0.4988894649257552</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="39">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="15">
+        <v>0.23869597547016905</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0.30423476563261509</v>
+      </c>
+      <c r="H44" s="15">
+        <v>0.45706925889721589</v>
+      </c>
+      <c r="I44" s="15">
+        <v>0.68964829676416761</v>
+      </c>
+      <c r="J44" s="15">
+        <v>0.55333760305007618</v>
+      </c>
+      <c r="K44" s="15">
+        <v>0.44102857740626561</v>
+      </c>
+      <c r="L44" s="15">
+        <v>0.56133815907350315</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86B53E65-A5CD-445A-867F-09955D746A05}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{045CB4B8-A54F-42EF-BF7B-03CBA01C39B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
@@ -676,6 +676,448 @@
   <dxfs count="32">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Consolas"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -691,7 +1133,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="#,##0%"/>
+      <numFmt numFmtId="164" formatCode="#,##0.0%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -699,21 +1141,15 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1080,13 +1516,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1103,104 +1532,9 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
+      <border>
         <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1221,7 +1555,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="#,##0.0%"/>
+      <numFmt numFmtId="165" formatCode="#,##0%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1229,355 +1563,21 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Consolas"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -1593,44 +1593,47 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{603625AB-3424-4720-B64C-3A94669BB298}" name="Tabla2" displayName="Tabla2" ref="A1:N41" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
-  <autoFilter ref="A1:N41" xr:uid="{603625AB-3424-4720-B64C-3A94669BB298}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{603625AB-3424-4720-B64C-3A94669BB298}" name="Tabla2" displayName="Tabla2" ref="A1:N41" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{C4951A27-4154-41B9-B8D4-A85237FF27BF}" name="PERÍODO" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{5E8E4C53-105C-4F0F-B81B-43DF12C5AD0C}" name="UNIDAD ACADÉMICA" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{1622C96A-86CF-4A32-88C0-A8FD0D98D6A4}" name="ASIGNATURA" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{AAE76B90-D559-4C6D-BCE8-2CB5914A2688}" name="ETAPA" dataDxfId="11" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{B27D401D-C4DB-4F5A-907B-A46E26DCD2EB}" name="NIVEL" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{82381162-CBF8-4ECF-B3AF-DA6791C58B9F}" name="NIVEL I" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{B10D23DF-EC5A-4F8C-AF44-37E67CAA187A}" name="NIVEL II" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{65D81586-5C35-48A1-9AC1-4470C0B6F64C}" name="NIVEL III" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{54F6FC8D-DFEF-4061-93FF-C58C6CAA5482}" name="num" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{A588398E-D9E2-47E2-A40D-A54D5A1F8777}" name="alg" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{24694D93-E6C0-4608-803B-1BBFBA44AFB1}" name="geo" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{28D83C33-2DC3-47CD-9ADC-F1FF73A0D836}" name="dat" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{2FD8D12D-E6C6-480D-9CEF-EE7BE8A525CC}" name="med" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{40066EBD-274C-4BC8-B1C6-81AF6378E2A8}" name="prom_mat" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C4951A27-4154-41B9-B8D4-A85237FF27BF}" name="PERÍODO" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{5E8E4C53-105C-4F0F-B81B-43DF12C5AD0C}" name="UNIDAD ACADÉMICA" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{1622C96A-86CF-4A32-88C0-A8FD0D98D6A4}" name="ASIGNATURA" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{AAE76B90-D559-4C6D-BCE8-2CB5914A2688}" name="ETAPA" dataDxfId="24" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{B27D401D-C4DB-4F5A-907B-A46E26DCD2EB}" name="NIVEL" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{82381162-CBF8-4ECF-B3AF-DA6791C58B9F}" name="NIVEL I" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{B10D23DF-EC5A-4F8C-AF44-37E67CAA187A}" name="NIVEL II" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{65D81586-5C35-48A1-9AC1-4470C0B6F64C}" name="NIVEL III" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{54F6FC8D-DFEF-4061-93FF-C58C6CAA5482}" name="num" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{A588398E-D9E2-47E2-A40D-A54D5A1F8777}" name="alg" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{24694D93-E6C0-4608-803B-1BBFBA44AFB1}" name="geo" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{28D83C33-2DC3-47CD-9ADC-F1FF73A0D836}" name="dat" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{2FD8D12D-E6C6-480D-9CEF-EE7BE8A525CC}" name="med" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{40066EBD-274C-4BC8-B1C6-81AF6378E2A8}" name="prom_mat" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BBE7D88-08B6-4227-B44B-6F2AACDCA85A}" name="Tabla1" displayName="Tabla1" ref="A1:L44" totalsRowShown="0" headerRowDxfId="21" dataDxfId="22" dataCellStyle="Porcentaje">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BBE7D88-08B6-4227-B44B-6F2AACDCA85A}" name="Tabla1" displayName="Tabla1" ref="A1:L44" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" dataCellStyle="Porcentaje">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{BFABC6FB-038F-4877-A79C-66D905599850}" name="PERÍODO" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{2A4B2E8A-F289-455C-8AF2-142A5B5039FA}" name="UNIDAD ACADÉMICA" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{75021AED-3042-4D7B-A073-F60F1DCB4EF4}" name="ASIGNATURA" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{AD981768-D01C-4F19-A096-A7441E4E5255}" name="ETAPA" dataDxfId="20" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{C59B8166-AA39-4643-8D4D-56C399243BF4}" name="NIVEL" dataDxfId="18" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{D2F2AB2A-0FB6-4DE1-963A-D22995224D52}" name="NIVEL I" dataDxfId="19" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{0D50C56D-C38A-4557-8265-DC6576552F9D}" name="NIVEL II" dataDxfId="28" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{001A79ED-9900-4053-90F8-0D8D7517B7EA}" name="NIVEL III" dataDxfId="27" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{40675EC1-4EDC-4294-ADD7-CD999FEEEE37}" name="loc" dataDxfId="26" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{07846A22-0AB6-49E3-8E77-E4DF29BC232E}" name="int" dataDxfId="25" dataCellStyle="Porcentaje"/>
-    <tableColumn id="11" xr3:uid="{824A9A32-EBF9-4D91-BCF1-21F5FB910191}" name="ref" dataDxfId="24" dataCellStyle="Porcentaje"/>
-    <tableColumn id="12" xr3:uid="{2FAFF1D1-ACFC-409D-980E-C4DD4A1272CF}" name="prom_len" dataDxfId="23" dataCellStyle="Porcentaje"/>
+    <tableColumn id="1" xr3:uid="{BFABC6FB-038F-4877-A79C-66D905599850}" name="PERÍODO" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{2A4B2E8A-F289-455C-8AF2-142A5B5039FA}" name="UNIDAD ACADÉMICA" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{75021AED-3042-4D7B-A073-F60F1DCB4EF4}" name="ASIGNATURA" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{AD981768-D01C-4F19-A096-A7441E4E5255}" name="ETAPA" dataDxfId="8" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{C59B8166-AA39-4643-8D4D-56C399243BF4}" name="NIVEL" dataDxfId="7" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{D2F2AB2A-0FB6-4DE1-963A-D22995224D52}" name="NIVEL I" dataDxfId="6" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{0D50C56D-C38A-4557-8265-DC6576552F9D}" name="NIVEL II" dataDxfId="5" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{001A79ED-9900-4053-90F8-0D8D7517B7EA}" name="NIVEL III" dataDxfId="4" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{40675EC1-4EDC-4294-ADD7-CD999FEEEE37}" name="loc" dataDxfId="3" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{07846A22-0AB6-49E3-8E77-E4DF29BC232E}" name="int" dataDxfId="2" dataCellStyle="Porcentaje"/>
+    <tableColumn id="11" xr3:uid="{824A9A32-EBF9-4D91-BCF1-21F5FB910191}" name="ref" dataDxfId="1" dataCellStyle="Porcentaje"/>
+    <tableColumn id="12" xr3:uid="{2FAFF1D1-ACFC-409D-980E-C4DD4A1272CF}" name="prom_len" dataDxfId="0" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8780,10 +8783,10 @@
         <v>0.73469387755102045</v>
       </c>
       <c r="L2" s="40">
+        <v>0.88436530612244912</v>
+      </c>
+      <c r="M2" s="40">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="M2" s="40">
-        <v>0.88436530612244912</v>
       </c>
       <c r="N2" s="51">
         <v>0.81318571428571418</v>
@@ -8824,10 +8827,10 @@
         <v>0.74444444444444446</v>
       </c>
       <c r="L3" s="40">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="M3" s="40">
         <v>0.65926666666666678</v>
-      </c>
-      <c r="M3" s="40">
-        <v>0.52222222222222225</v>
       </c>
       <c r="N3" s="51">
         <v>0.60313111111111128</v>
@@ -8868,10 +8871,10 @@
         <v>0.75</v>
       </c>
       <c r="L4" s="40">
+        <v>0.625</v>
+      </c>
+      <c r="M4" s="40">
         <v>0.34166666666666662</v>
-      </c>
-      <c r="M4" s="40">
-        <v>0.625</v>
       </c>
       <c r="N4" s="51">
         <v>0.57228749999999995</v>
@@ -8912,10 +8915,10 @@
         <v>0.55556419753086439</v>
       </c>
       <c r="L5" s="40">
+        <v>0.37036543209876532</v>
+      </c>
+      <c r="M5" s="40">
         <v>0.31790123456790126</v>
-      </c>
-      <c r="M5" s="40">
-        <v>0.37036543209876532</v>
       </c>
       <c r="N5" s="51">
         <v>0.41463703703703692</v>
@@ -8956,10 +8959,10 @@
         <v>0.4642857142857143</v>
       </c>
       <c r="L6" s="40">
+        <v>0.50510204081632648</v>
+      </c>
+      <c r="M6" s="40">
         <v>0.28571428571428575</v>
-      </c>
-      <c r="M6" s="40">
-        <v>0.50510204081632648</v>
       </c>
       <c r="N6" s="51">
         <v>0.46216326530612245</v>
@@ -9000,11 +9003,9 @@
         <v>0.359375</v>
       </c>
       <c r="L7" s="40">
-        <v>0</v>
-      </c>
-      <c r="M7" s="40">
         <v>0.32031093749999989</v>
       </c>
+      <c r="M7" s="40"/>
       <c r="N7" s="51">
         <v>0.34389999999999993</v>
       </c>
@@ -9044,10 +9045,10 @@
         <v>0.58642407407407415</v>
       </c>
       <c r="L8" s="40">
+        <v>0.73148148148148151</v>
+      </c>
+      <c r="M8" s="40">
         <v>0.66203703703703709</v>
-      </c>
-      <c r="M8" s="40">
-        <v>0.73148148148148151</v>
       </c>
       <c r="N8" s="51">
         <v>0.59564259259259256</v>
@@ -9088,10 +9089,10 @@
         <v>0.31147540983606559</v>
       </c>
       <c r="L9" s="40">
+        <v>0.68032786885245899</v>
+      </c>
+      <c r="M9" s="40">
         <v>0.63934426229508201</v>
-      </c>
-      <c r="M9" s="40">
-        <v>0.68032786885245899</v>
       </c>
       <c r="N9" s="51">
         <v>0.53711147540983606</v>
@@ -9132,10 +9133,10 @@
         <v>0.56785714285714284</v>
       </c>
       <c r="L10" s="40">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="M10" s="40">
         <v>0.6753985714285714</v>
-      </c>
-      <c r="M10" s="40">
-        <v>0.42857142857142855</v>
       </c>
       <c r="N10" s="51">
         <v>0.46339714285714295</v>
@@ -9176,10 +9177,10 @@
         <v>0.69872788461538482</v>
       </c>
       <c r="L11" s="40">
+        <v>0.453125</v>
+      </c>
+      <c r="M11" s="40">
         <v>0.53526153846153857</v>
-      </c>
-      <c r="M11" s="40">
-        <v>0.453125</v>
       </c>
       <c r="N11" s="51">
         <v>0.53565576923076941</v>
@@ -9220,11 +9221,9 @@
         <v>0.54885603448275877</v>
       </c>
       <c r="L12" s="40">
-        <v>0</v>
-      </c>
-      <c r="M12" s="40">
         <v>0.44181034482758619</v>
       </c>
+      <c r="M12" s="40"/>
       <c r="N12" s="51">
         <v>0.45297068965517229</v>
       </c>
@@ -9264,11 +9263,9 @@
         <v>0.46586325301204817</v>
       </c>
       <c r="L13" s="40">
-        <v>0</v>
-      </c>
-      <c r="M13" s="40">
         <v>0.57028192771084341</v>
       </c>
+      <c r="M13" s="40"/>
       <c r="N13" s="51">
         <v>0.5172674698795181</v>
       </c>
@@ -9308,10 +9305,10 @@
         <v>0.71296296296296291</v>
       </c>
       <c r="L14" s="40">
+        <v>0.70372037037037061</v>
+      </c>
+      <c r="M14" s="40">
         <v>0.85185185185185186</v>
-      </c>
-      <c r="M14" s="40">
-        <v>0.70372037037037061</v>
       </c>
       <c r="N14" s="51">
         <v>0.75516851851851829</v>
@@ -9352,10 +9349,10 @@
         <v>0.77777777777777768</v>
       </c>
       <c r="L15" s="40">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="M15" s="40">
         <v>0.54074222222222201</v>
-      </c>
-      <c r="M15" s="40">
-        <v>0.4777777777777778</v>
       </c>
       <c r="N15" s="51">
         <v>0.55323111111111101</v>
@@ -9396,10 +9393,10 @@
         <v>0.62096774193548387</v>
       </c>
       <c r="L16" s="40">
+        <v>0.66935483870967749</v>
+      </c>
+      <c r="M16" s="40">
         <v>0.3612903225806452</v>
-      </c>
-      <c r="M16" s="40">
-        <v>0.66935483870967749</v>
       </c>
       <c r="N16" s="51">
         <v>0.55311290322580631</v>
@@ -9440,10 +9437,10 @@
         <v>0.59204925373134332</v>
       </c>
       <c r="L17" s="40">
+        <v>0.56716417910447769</v>
+      </c>
+      <c r="M17" s="40">
         <v>0.30970149253731344</v>
-      </c>
-      <c r="M17" s="40">
-        <v>0.56716417910447769</v>
       </c>
       <c r="N17" s="51">
         <v>0.49101343283582083</v>
@@ -9484,10 +9481,10 @@
         <v>0.31770833333333331</v>
       </c>
       <c r="L18" s="40">
+        <v>0.5859375</v>
+      </c>
+      <c r="M18" s="40">
         <v>0.1875</v>
-      </c>
-      <c r="M18" s="40">
-        <v>0.5859375</v>
       </c>
       <c r="N18" s="51">
         <v>0.4223229166666666</v>
@@ -9528,11 +9525,9 @@
         <v>0.4</v>
       </c>
       <c r="L19" s="40">
-        <v>0</v>
-      </c>
-      <c r="M19" s="40">
         <v>0.50277500000000008</v>
       </c>
+      <c r="M19" s="40"/>
       <c r="N19" s="51">
         <v>0.45980666666666664</v>
       </c>
@@ -9572,10 +9567,10 @@
         <v>0.69565434782608704</v>
       </c>
       <c r="L20" s="40">
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="M20" s="40">
         <v>0.61956521739130432</v>
-      </c>
-      <c r="M20" s="40">
-        <v>0.73913043478260876</v>
       </c>
       <c r="N20" s="51">
         <v>0.61596956521739121</v>
@@ -9616,10 +9611,10 @@
         <v>0.25</v>
       </c>
       <c r="L21" s="40">
+        <v>0.63392857142857151</v>
+      </c>
+      <c r="M21" s="40">
         <v>0.5625</v>
-      </c>
-      <c r="M21" s="40">
-        <v>0.63392857142857151</v>
       </c>
       <c r="N21" s="51">
         <v>0.48342321428571433</v>
@@ -9660,10 +9655,10 @@
         <v>0.56153846153846154</v>
       </c>
       <c r="L22" s="40">
+        <v>0.39743589743589747</v>
+      </c>
+      <c r="M22" s="40">
         <v>0.58632615384615383</v>
-      </c>
-      <c r="M22" s="40">
-        <v>0.39743589743589747</v>
       </c>
       <c r="N22" s="51">
         <v>0.41245999999999972</v>
@@ -9704,10 +9699,10 @@
         <v>0.61538846153846161</v>
       </c>
       <c r="L23" s="40">
+        <v>0.52884615384615385</v>
+      </c>
+      <c r="M23" s="40">
         <v>0.49487615384615391</v>
-      </c>
-      <c r="M23" s="40">
-        <v>0.52884615384615385</v>
       </c>
       <c r="N23" s="51">
         <v>0.48882923076923068</v>
@@ -9748,11 +9743,9 @@
         <v>0.51239256756756768</v>
       </c>
       <c r="L24" s="40">
-        <v>0</v>
-      </c>
-      <c r="M24" s="40">
         <v>0.42539324324324318</v>
       </c>
+      <c r="M24" s="40"/>
       <c r="N24" s="51">
         <v>0.43634324324324325</v>
       </c>
@@ -9792,11 +9785,9 @@
         <v>0.51598082191780814</v>
       </c>
       <c r="L25" s="40">
-        <v>0</v>
-      </c>
-      <c r="M25" s="40">
         <v>0.54490091324200907</v>
       </c>
+      <c r="M25" s="40"/>
       <c r="N25" s="51">
         <v>0.54200821917808217</v>
       </c>
@@ -9836,10 +9827,10 @@
         <v>0.60365853658536583</v>
       </c>
       <c r="L26" s="40">
+        <v>0.68293658536585378</v>
+      </c>
+      <c r="M26" s="40">
         <v>0.71951219512195119</v>
-      </c>
-      <c r="M26" s="40">
-        <v>0.68293658536585378</v>
       </c>
       <c r="N26" s="51">
         <v>0.65779512195121925</v>
@@ -9880,10 +9871,10 @@
         <v>0.81632653061224492</v>
       </c>
       <c r="L27" s="40">
+        <v>0.60714285714285721</v>
+      </c>
+      <c r="M27" s="40">
         <v>0.5782326530612244</v>
-      </c>
-      <c r="M27" s="40">
-        <v>0.60714285714285721</v>
       </c>
       <c r="N27" s="51">
         <v>0.69327142857142843</v>
@@ -9924,10 +9915,10 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="L28" s="40">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="M28" s="40">
         <v>0.56666666666666665</v>
-      </c>
-      <c r="M28" s="40">
-        <v>0.7416666666666667</v>
       </c>
       <c r="N28" s="51">
         <v>0.69382333333333379</v>
@@ -9968,10 +9959,10 @@
         <v>0.58823781512605045</v>
       </c>
       <c r="L29" s="40">
+        <v>0.49019411764705878</v>
+      </c>
+      <c r="M29" s="40">
         <v>0.35714285714285715</v>
-      </c>
-      <c r="M29" s="40">
-        <v>0.49019411764705878</v>
       </c>
       <c r="N29" s="51">
         <v>0.47792521008403355</v>
@@ -10012,10 +10003,10 @@
         <v>0.71846846846846846</v>
       </c>
       <c r="L30" s="40">
+        <v>0.60923423423423417</v>
+      </c>
+      <c r="M30" s="40">
         <v>0.55630630630630629</v>
-      </c>
-      <c r="M30" s="40">
-        <v>0.60923423423423417</v>
       </c>
       <c r="N30" s="51">
         <v>0.66470540540540579</v>
@@ -10056,11 +10047,9 @@
         <v>0.40336134453781514</v>
       </c>
       <c r="L31" s="40">
-        <v>0</v>
-      </c>
-      <c r="M31" s="40">
         <v>0.39775966386554612</v>
       </c>
+      <c r="M31" s="40"/>
       <c r="N31" s="51">
         <v>0.41104789915966372</v>
       </c>
@@ -10100,10 +10089,10 @@
         <v>0.5360364864864865</v>
       </c>
       <c r="L32" s="40">
+        <v>0.69594594594594594</v>
+      </c>
+      <c r="M32" s="40">
         <v>0.6283783783783784</v>
-      </c>
-      <c r="M32" s="40">
-        <v>0.69594594594594594</v>
       </c>
       <c r="N32" s="51">
         <v>0.56560135135135114</v>
@@ -10144,10 +10133,10 @@
         <v>0.57291666666666663</v>
       </c>
       <c r="L33" s="40">
+        <v>0.78645833333333326</v>
+      </c>
+      <c r="M33" s="40">
         <v>0.75</v>
-      </c>
-      <c r="M33" s="40">
-        <v>0.78645833333333326</v>
       </c>
       <c r="N33" s="51">
         <v>0.6467197916666666</v>
@@ -10188,10 +10177,10 @@
         <v>0.56640625</v>
       </c>
       <c r="L34" s="40">
+        <v>0.45963541666666663</v>
+      </c>
+      <c r="M34" s="40">
         <v>0.56423776041666618</v>
-      </c>
-      <c r="M34" s="40">
-        <v>0.45963541666666663</v>
       </c>
       <c r="N34" s="51">
         <v>0.45111718749999979</v>
@@ -10232,10 +10221,10 @@
         <v>0.77865234374999914</v>
       </c>
       <c r="L35" s="40">
+        <v>0.6845703125</v>
+      </c>
+      <c r="M35" s="40">
         <v>0.66536875000000006</v>
-      </c>
-      <c r="M35" s="40">
-        <v>0.6845703125</v>
       </c>
       <c r="N35" s="51">
         <v>0.69423203124999988</v>
@@ -10276,11 +10265,9 @@
         <v>0.72580766129032237</v>
       </c>
       <c r="L36" s="40">
-        <v>0</v>
-      </c>
-      <c r="M36" s="40">
         <v>0.56955685483870966</v>
       </c>
+      <c r="M36" s="40"/>
       <c r="N36" s="51">
         <v>0.5802459677419356</v>
       </c>
@@ -10320,11 +10307,9 @@
         <v>0.53165542635658913</v>
       </c>
       <c r="L37" s="40">
-        <v>0</v>
-      </c>
-      <c r="M37" s="40">
         <v>0.59538888888888908</v>
       </c>
+      <c r="M37" s="40"/>
       <c r="N37" s="40">
         <v>0.57171782945736438</v>
       </c>

--- a/src/pages/data/data_dia_2024.xlsx
+++ b/src/pages/data/data_dia_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CEDD422-95CF-44C7-A9B7-A6394C842A41}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{5EE33713-D912-4866-B300-568C29DC986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29141F88-81F4-52BF-858A-DC61604888C7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="4455" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dia_mat" sheetId="1" r:id="rId1"/>
@@ -555,10 +555,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -848,21 +844,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -900,7 +896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -939,7 +935,7 @@
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -978,7 +974,7 @@
         <v>0.377</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -1056,7 +1052,7 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
@@ -1095,7 +1091,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
@@ -1134,7 +1130,7 @@
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -1173,7 +1169,7 @@
         <v>0.26800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
@@ -1212,7 +1208,7 @@
         <v>0.17299999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -1251,7 +1247,7 @@
         <v>0.36099999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
@@ -1290,7 +1286,7 @@
         <v>0.29399999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -1329,7 +1325,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
@@ -1368,7 +1364,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
@@ -1407,7 +1403,7 @@
         <v>0.28499999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -1446,7 +1442,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
@@ -1485,7 +1481,7 @@
         <v>0.372</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
@@ -1524,7 +1520,7 @@
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
@@ -1563,7 +1559,7 @@
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
@@ -1602,7 +1598,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
@@ -1641,7 +1637,7 @@
         <v>0.42699999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
@@ -1680,7 +1676,7 @@
         <v>0.32300000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>17</v>
       </c>
@@ -1719,7 +1715,7 @@
         <v>0.38800000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>18</v>
       </c>
@@ -1758,7 +1754,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>19</v>
       </c>
@@ -1797,7 +1793,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>20</v>
       </c>
@@ -1836,7 +1832,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>22</v>
       </c>
@@ -1875,7 +1871,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>23</v>
       </c>
@@ -1914,7 +1910,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>24</v>
       </c>
@@ -1953,7 +1949,7 @@
         <v>0.36899999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>25</v>
       </c>
@@ -1992,7 +1988,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2027,7 @@
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>27</v>
       </c>
@@ -2070,7 +2066,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>28</v>
       </c>
@@ -2116,7 +2112,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>29</v>
       </c>
@@ -2162,7 +2158,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>28</v>
       </c>
@@ -2208,7 +2204,7 @@
         <v>0.376</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>29</v>
       </c>
@@ -2254,7 +2250,7 @@
         <v>0.33700000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>10</v>
       </c>
@@ -2293,7 +2289,7 @@
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>13</v>
       </c>
@@ -2332,7 +2328,7 @@
         <v>0.377</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +2367,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>15</v>
       </c>
@@ -2410,7 +2406,7 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>16</v>
       </c>
@@ -2449,7 +2445,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>17</v>
       </c>
@@ -2488,7 +2484,7 @@
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>18</v>
       </c>
@@ -2527,7 +2523,7 @@
         <v>0.26800000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>19</v>
       </c>
@@ -2566,7 +2562,7 @@
         <v>0.17299999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>20</v>
       </c>
@@ -2605,7 +2601,7 @@
         <v>0.36099999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>22</v>
       </c>
@@ -2644,7 +2640,7 @@
         <v>0.29399999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>23</v>
       </c>
@@ -2683,7 +2679,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>24</v>
       </c>
@@ -2722,7 +2718,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>25</v>
       </c>
@@ -2761,7 +2757,7 @@
         <v>0.28499999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>26</v>
       </c>
@@ -2800,7 +2796,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>27</v>
       </c>
@@ -2839,7 +2835,7 @@
         <v>0.372</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>10</v>
       </c>
@@ -2878,7 +2874,7 @@
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>13</v>
       </c>
@@ -2917,7 +2913,7 @@
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>14</v>
       </c>
@@ -2956,7 +2952,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>15</v>
       </c>
@@ -2995,7 +2991,7 @@
         <v>0.42699999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>16</v>
       </c>
@@ -3034,7 +3030,7 @@
         <v>0.32300000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>17</v>
       </c>
@@ -3073,7 +3069,7 @@
         <v>0.38800000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>18</v>
       </c>
@@ -3112,7 +3108,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>19</v>
       </c>
@@ -3151,7 +3147,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>20</v>
       </c>
@@ -3190,7 +3186,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>22</v>
       </c>
@@ -3229,7 +3225,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>23</v>
       </c>
@@ -3268,7 +3264,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>24</v>
       </c>
@@ -3307,7 +3303,7 @@
         <v>0.36899999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>25</v>
       </c>
@@ -3346,7 +3342,7 @@
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>26</v>
       </c>
@@ -3385,7 +3381,7 @@
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>27</v>
       </c>
@@ -3424,7 +3420,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>28</v>
       </c>
@@ -3470,7 +3466,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>29</v>
       </c>
@@ -3516,7 +3512,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>28</v>
       </c>
@@ -3562,7 +3558,7 @@
         <v>0.376</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>29</v>
       </c>
@@ -3619,20 +3615,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -3667,7 +3663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -3703,7 +3699,7 @@
         <v>0.69199999999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -3739,7 +3735,7 @@
         <v>0.71499999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -3775,7 +3771,7 @@
         <v>0.66500000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -3811,7 +3807,7 @@
         <v>0.68200000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
@@ -3847,7 +3843,7 @@
         <v>0.69199999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
@@ -3883,7 +3879,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -3919,7 +3915,7 @@
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
@@ -3955,7 +3951,7 @@
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -3991,7 +3987,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
@@ -4027,7 +4023,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -4063,7 +4059,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
@@ -4099,7 +4095,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
@@ -4135,7 +4131,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -4171,7 +4167,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
@@ -4207,7 +4203,7 @@
         <v>0.76700000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
@@ -4243,7 +4239,7 @@
         <v>0.69799999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
@@ -4279,7 +4275,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
@@ -4315,7 +4311,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
@@ -4351,7 +4347,7 @@
         <v>0.67800000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
@@ -4387,7 +4383,7 @@
         <v>0.59899999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>17</v>
       </c>
@@ -4423,7 +4419,7 @@
         <v>0.68400000000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>18</v>
       </c>
@@ -4459,7 +4455,7 @@
         <v>0.56599999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>19</v>
       </c>
@@ -4495,7 +4491,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>20</v>
       </c>
@@ -4531,7 +4527,7 @@
         <v>0.67100000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>22</v>
       </c>
@@ -4567,7 +4563,7 @@
         <v>0.629</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>23</v>
       </c>
@@ -4603,7 +4599,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>24</v>
       </c>
@@ -4639,7 +4635,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>25</v>
       </c>
@@ -4675,7 +4671,7 @@
         <v>0.55400000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>26</v>
       </c>
@@ -4711,7 +4707,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>27</v>
       </c>
@@ -4747,7 +4743,7 @@
         <v>0.74399999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>28</v>
       </c>
@@ -4789,7 +4785,7 @@
         <v>0.65400000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>29</v>
       </c>
@@ -4831,7 +4827,7 @@
         <v>0.64100000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>28</v>
       </c>
@@ -4873,7 +4869,7 @@
         <v>0.64500000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>29</v>
       </c>
@@ -4915,7 +4911,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>10</v>
       </c>
@@ -4951,7 +4947,7 @@
         <v>0.69199999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>13</v>
       </c>
@@ -4987,7 +4983,7 @@
         <v>0.71499999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>14</v>
       </c>
@@ -5023,7 +5019,7 @@
         <v>0.66500000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>15</v>
       </c>
@@ -5059,7 +5055,7 @@
         <v>0.68200000000000005</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>16</v>
       </c>
@@ -5095,7 +5091,7 @@
         <v>0.69199999999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>17</v>
       </c>
@@ -5131,7 +5127,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>18</v>
       </c>
@@ -5167,7 +5163,7 @@
         <v>0.60099999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>19</v>
       </c>
@@ -5203,7 +5199,7 @@
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>20</v>
       </c>
@@ -5239,7 +5235,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>22</v>
       </c>
@@ -5275,7 +5271,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>23</v>
       </c>
@@ -5311,7 +5307,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>24</v>
       </c>
@@ -5347,7 +5343,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>25</v>
       </c>
@@ -5383,7 +5379,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>26</v>
       </c>
@@ -5419,7 +5415,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>27</v>
       </c>
@@ -5455,7 +5451,7 @@
         <v>0.76700000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>10</v>
       </c>
@@ -5491,7 +5487,7 @@
         <v>0.69799999999999995</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>13</v>
       </c>
@@ -5527,7 +5523,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>14</v>
       </c>
@@ -5563,7 +5559,7 @@
         <v>0.70299999999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>15</v>
       </c>
@@ -5599,7 +5595,7 @@
         <v>0.67800000000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>16</v>
       </c>
@@ -5635,7 +5631,7 @@
         <v>0.59899999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>17</v>
       </c>
@@ -5671,7 +5667,7 @@
         <v>0.68400000000000005</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>18</v>
       </c>
@@ -5707,7 +5703,7 @@
         <v>0.56599999999999995</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>19</v>
       </c>
@@ -5743,7 +5739,7 @@
         <v>0.52900000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>20</v>
       </c>
@@ -5779,7 +5775,7 @@
         <v>0.67100000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>22</v>
       </c>
@@ -5815,7 +5811,7 @@
         <v>0.629</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>23</v>
       </c>
@@ -5851,7 +5847,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>24</v>
       </c>
@@ -5887,7 +5883,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>25</v>
       </c>
@@ -5923,7 +5919,7 @@
         <v>0.55400000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>26</v>
       </c>
@@ -5959,7 +5955,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>27</v>
       </c>
@@ -5995,7 +5991,7 @@
         <v>0.74399999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>28</v>
       </c>
@@ -6037,7 +6033,7 @@
         <v>0.65400000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>29</v>
       </c>
@@ -6079,7 +6075,7 @@
         <v>0.64100000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>28</v>
       </c>
@@ -6121,7 +6117,7 @@
         <v>0.64500000000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>29</v>
       </c>
@@ -6177,20 +6173,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>39</v>
       </c>
@@ -6231,7 +6227,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25"/>
       <c r="B2" s="27"/>
       <c r="C2" s="24" t="s">
@@ -6274,7 +6270,7 @@
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
     </row>
-    <row r="3" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="25"/>
       <c r="B3" s="27"/>
       <c r="C3" s="24" t="s">
@@ -6317,7 +6313,7 @@
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="27"/>
       <c r="C4" s="24" t="s">
@@ -6360,7 +6356,7 @@
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
     </row>
-    <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25"/>
       <c r="B5" s="27"/>
       <c r="C5" s="24" t="s">
@@ -6403,7 +6399,7 @@
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
     </row>
-    <row r="6" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
       <c r="B6" s="27"/>
       <c r="C6" s="24" t="s">
@@ -6446,7 +6442,7 @@
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25"/>
       <c r="B7" s="27"/>
       <c r="C7" s="24" t="s">
@@ -6489,7 +6485,7 @@
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
     </row>
-    <row r="8" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25"/>
       <c r="B8" s="27"/>
       <c r="C8" s="24" t="s">
@@ -6532,7 +6528,7 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25"/>
       <c r="B9" s="27"/>
       <c r="C9" s="24" t="s">
@@ -6575,7 +6571,7 @@
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
     </row>
-    <row r="10" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
       <c r="B10" s="27"/>
       <c r="C10" s="24" t="s">
@@ -6618,7 +6614,7 @@
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25"/>
       <c r="B11" s="27"/>
       <c r="C11" s="24" t="s">
@@ -6661,7 +6657,7 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
     </row>
-    <row r="12" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
       <c r="B12" s="27"/>
       <c r="C12" s="24" t="s">
@@ -6704,7 +6700,7 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25"/>
       <c r="B13" s="27"/>
       <c r="C13" s="24" t="s">
@@ -6747,7 +6743,7 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
     </row>
-    <row r="14" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
       <c r="B14" s="27"/>
       <c r="C14" s="24" t="s">
@@ -6790,7 +6786,7 @@
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
     </row>
-    <row r="15" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
       <c r="B15" s="27"/>
       <c r="C15" s="24" t="s">
@@ -6833,7 +6829,7 @@
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
     </row>
-    <row r="16" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25"/>
       <c r="B16" s="27"/>
       <c r="C16" s="24" t="s">
@@ -6876,7 +6872,7 @@
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
     </row>
-    <row r="17" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25"/>
       <c r="B17" s="27"/>
       <c r="C17" s="24" t="s">
@@ -6926,7 +6922,7 @@
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
     </row>
-    <row r="18" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25"/>
       <c r="B18" s="27"/>
       <c r="C18" s="24" t="s">
@@ -6990,14 +6986,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7029,7 +7025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -7062,7 +7058,7 @@
         <v>0.52200000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -7095,7 +7091,7 @@
         <v>0.66100000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -7128,7 +7124,7 @@
         <v>0.622</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -7161,7 +7157,7 @@
         <v>0.56899999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
@@ -7194,7 +7190,7 @@
         <v>0.60499999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
@@ -7227,7 +7223,7 @@
         <v>0.53300000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -7260,7 +7256,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
@@ -7293,7 +7289,7 @@
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -7326,7 +7322,7 @@
         <v>0.63700000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
@@ -7359,7 +7355,7 @@
         <v>0.63700000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -7392,7 +7388,7 @@
         <v>0.55500000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
@@ -7425,7 +7421,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
@@ -7458,7 +7454,7 @@
         <v>0.52600000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -7491,7 +7487,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
@@ -7524,7 +7520,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>28</v>
       </c>
@@ -7563,7 +7559,7 @@
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
@@ -7613,16 +7609,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C54D2E6-D3E1-4CCD-A700-1303E31935A9}">
   <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>39</v>
       </c>
@@ -7666,7 +7662,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>2026</v>
       </c>
@@ -7710,7 +7706,7 @@
         <v>0.81318571428571418</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2026</v>
       </c>
@@ -7754,7 +7750,7 @@
         <v>0.60313111111111128</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>2026</v>
       </c>
@@ -7798,7 +7794,7 @@
         <v>0.57228749999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>2026</v>
       </c>
@@ -7842,7 +7838,7 @@
         <v>0.41463703703703692</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>2026</v>
       </c>
@@ -7886,7 +7882,7 @@
         <v>0.46216326530612245</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>2026</v>
       </c>
@@ -7930,7 +7926,7 @@
         <v>0.34389999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2026</v>
       </c>
@@ -7974,7 +7970,7 @@
         <v>0.59564259259259256</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>2026</v>
       </c>
@@ -8018,7 +8014,7 @@
         <v>0.53711147540983606</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>2026</v>
       </c>
@@ -8062,7 +8058,7 @@
         <v>0.46339714285714295</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>2026</v>
       </c>
@@ -8106,7 +8102,7 @@
         <v>0.53565576923076941</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>2026</v>
       </c>
@@ -8150,7 +8146,7 @@
         <v>0.45297068965517229</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>2026</v>
       </c>
@@ -8194,7 +8190,7 @@
         <v>0.5172674698795181</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>2026</v>
       </c>
@@ -8238,7 +8234,7 @@
         <v>0.75516851851851829</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>2026</v>
       </c>
@@ -8282,7 +8278,7 @@
         <v>0.55323111111111101</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>2026</v>
       </c>
@@ -8326,7 +8322,7 @@
         <v>0.55311290322580631</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>2026</v>
       </c>
@@ -8370,7 +8366,7 @@
         <v>0.49101343283582083</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>2026</v>
       </c>
@@ -8414,7 +8410,7 @@
         <v>0.4223229166666666</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>2026</v>
       </c>
@@ -8458,7 +8454,7 @@
         <v>0.45980666666666664</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>2026</v>
       </c>
@@ -8502,7 +8498,7 @@
         <v>0.61596956521739121</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>2026</v>
       </c>
@@ -8546,7 +8542,7 @@
         <v>0.48342321428571433</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>2026</v>
       </c>
@@ -8590,7 +8586,7 @@
         <v>0.41245999999999972</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>2026</v>
       </c>
@@ -8634,7 +8630,7 @@
         <v>0.48882923076923068</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>2026</v>
       </c>
@@ -8678,7 +8674,7 @@
         <v>0.43634324324324325</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>2026</v>
       </c>
@@ -8722,7 +8718,7 @@
         <v>0.54200821917808217</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>2026</v>
       </c>
@@ -8766,7 +8762,7 @@
         <v>0.65779512195121925</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>2026</v>
       </c>
@@ -8810,7 +8806,7 @@
         <v>0.69327142857142843</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>2026</v>
       </c>
@@ -8854,7 +8850,7 @@
         <v>0.69382333333333379</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>2026</v>
       </c>
@@ -8898,7 +8894,7 @@
         <v>0.47792521008403355</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>2026</v>
       </c>
@@ -8942,7 +8938,7 @@
         <v>0.66470540540540579</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>2026</v>
       </c>
@@ -8986,7 +8982,7 @@
         <v>0.41104789915966372</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>2026</v>
       </c>
@@ -9030,7 +9026,7 @@
         <v>0.56560135135135114</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>2026</v>
       </c>
@@ -9074,7 +9070,7 @@
         <v>0.6467197916666666</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>2026</v>
       </c>
@@ -9118,7 +9114,7 @@
         <v>0.45111718749999979</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>2026</v>
       </c>
@@ -9162,7 +9158,7 @@
         <v>0.69423203124999988</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>2026</v>
       </c>
@@ -9206,7 +9202,7 @@
         <v>0.5802459677419356</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>2026</v>
       </c>
@@ -9258,14 +9254,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8147AE5B-C20B-4DEF-A7F6-B50B97C6DCC0}">
   <dimension ref="A1:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>39</v>
       </c>
@@ -9303,7 +9299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>2026</v>
       </c>
@@ -9341,7 +9337,7 @@
         <v>0.62944600000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2026</v>
       </c>
@@ -9379,7 +9375,7 @@
         <v>0.7018859999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>2026</v>
       </c>
@@ -9417,7 +9413,7 @@
         <v>0.63311186440677969</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>2026</v>
       </c>
@@ -9455,7 +9451,7 @@
         <v>0.50486989247311842</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>2026</v>
       </c>
@@ -9493,7 +9489,7 @@
         <v>0.56692881355932234</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>2026</v>
       </c>
@@ -9531,7 +9527,7 @@
         <v>0.54754459459459459</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2026</v>
       </c>
@@ -9569,7 +9565,7 @@
         <v>0.55176097560975623</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>2026</v>
       </c>
@@ -9607,7 +9603,7 @@
         <v>0.48179666666666665</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>2026</v>
       </c>
@@ -9645,7 +9641,7 @@
         <v>0.70125483870967753</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>2026</v>
       </c>
@@ -9683,7 +9679,7 @@
         <v>0.6310399999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>2026</v>
       </c>
@@ -9721,7 +9717,7 @@
         <v>0.5123392523364485</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>2026</v>
       </c>
@@ -9759,7 +9755,7 @@
         <v>0.55837258064516138</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>2026</v>
       </c>
@@ -9797,7 +9793,7 @@
         <v>0.57944249999999986</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>2026</v>
       </c>
@@ -9835,7 +9831,7 @@
         <v>0.69052352941176465</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>2026</v>
       </c>
@@ -9873,7 +9869,7 @@
         <v>0.51598775510204087</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>2026</v>
       </c>
@@ -9911,7 +9907,7 @@
         <v>0.54613035714285718</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>2026</v>
       </c>
@@ -9949,7 +9945,7 @@
         <v>0.58657735849056603</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>2026</v>
       </c>
@@ -9987,7 +9983,7 @@
         <v>0.52617272727272735</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>2026</v>
       </c>
@@ -10025,7 +10021,7 @@
         <v>0.51663880597014922</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>2026</v>
       </c>
@@ -10063,7 +10059,7 @@
         <v>0.65833499999999989</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>2026</v>
       </c>
@@ -10101,7 +10097,7 @@
         <v>0.55981428571428582</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>2026</v>
       </c>
@@ -10139,7 +10135,7 @@
         <v>0.62526078431372545</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>2026</v>
       </c>
@@ -10177,7 +10173,7 @@
         <v>0.54439830508474574</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>2026</v>
       </c>
@@ -10215,7 +10211,7 @@
         <v>0.51792112676056345</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>2026</v>
       </c>
@@ -10253,7 +10249,7 @@
         <v>0.50499344262295087</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>2026</v>
       </c>
@@ -10291,7 +10287,7 @@
         <v>0.5971209876543212</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>2026</v>
       </c>
@@ -10329,7 +10325,7 @@
         <v>0.58644390243902422</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>2026</v>
       </c>
@@ -10367,7 +10363,7 @@
         <v>0.7308154639175255</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>2026</v>
       </c>
@@ -10405,7 +10401,7 @@
         <v>0.66730550458715587</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>2026</v>
       </c>
@@ -10443,7 +10439,7 @@
         <v>0.66125865384615423</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>2026</v>
       </c>
@@ -10481,7 +10477,7 @@
         <v>0.63457289719626153</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>2026</v>
       </c>
@@ -10519,7 +10515,7 @@
         <v>0.62306249999999974</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>2026</v>
       </c>
@@ -10557,7 +10553,7 @@
         <v>0.52360000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>2026</v>
       </c>
@@ -10595,7 +10591,7 @@
         <v>0.52884109589041084</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>2026</v>
       </c>
@@ -10633,7 +10629,7 @@
         <v>0.77722323232323265</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>2026</v>
       </c>
@@ -10671,7 +10667,7 @@
         <v>0.67480692307692325</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>2026</v>
       </c>
@@ -10709,7 +10705,7 @@
         <v>0.70471226415094324</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>2026</v>
       </c>
@@ -10747,7 +10743,7 @@
         <v>0.51856666666666673</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>2026</v>
       </c>
